--- a/Global+Electronics+Retailer/Excel_Files/Revenue_Forecast.xlsx
+++ b/Global+Electronics+Retailer/Excel_Files/Revenue_Forecast.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Darren Cruz\Documents\Data Projects\Global+Electronics+Retailer\Excel_Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Darren Cruz\Documents\GitHub\Global-Electronics-Retail-Performace-Analysis\Global+Electronics+Retailer\Excel_Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C2D0B6-292B-4AFC-9B30-5F50D9091059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE5CAE03-3375-403B-AF2C-67669164EA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CAC95C2E-2B41-4FED-8B73-E3EFD4DDAC30}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="79">
   <si>
     <t>Month</t>
   </si>
@@ -178,18 +178,6 @@
     <t>1. The last month used to estimate indeces is July 2019, so that no 2020 data enters the seasonal trend.</t>
   </si>
   <si>
-    <t>4. The deseasonalized level persists (average of the last 3 months), with no recovery nor further decline.</t>
-  </si>
-  <si>
-    <t>5. The 2016-2019 seasonal patterns still hold.</t>
-  </si>
-  <si>
-    <t>2. The growth rate returns to its pace similar to the year 2019, that is +3% a month.</t>
-  </si>
-  <si>
-    <t>3. The 2020 declines continues at a milder rate than 2020,  that is -2% a month. A steeper decline can also be considered.</t>
-  </si>
-  <si>
     <t>Forecast = seasonal index * deseasonalized level * (1 + monthly growth)^n</t>
   </si>
   <si>
@@ -253,12 +241,6 @@
     <t>Values (USD)</t>
   </si>
   <si>
-    <t>Scalar factor</t>
-  </si>
-  <si>
-    <t>Average (Jan 2016 -Feb 2021</t>
-  </si>
-  <si>
     <t>Total</t>
   </si>
   <si>
@@ -293,6 +275,30 @@
   <si>
     <t>Here are the results using the built-in Excel forecast function.</t>
   </si>
+  <si>
+    <t>3. The growth rate returns to its pace similar to the year 2019, that is +3% a month.</t>
+  </si>
+  <si>
+    <t>4. The 2020 declines continues at a milder rate than 2020,  that is -2% a month. A steeper decline can also be considered.</t>
+  </si>
+  <si>
+    <t>5. The deseasonalized level persists (average of the last 3 months), with no recovery nor further decline.</t>
+  </si>
+  <si>
+    <t>6. The 2016-2019 seasonal patterns still hold.</t>
+  </si>
+  <si>
+    <t>Scale factor</t>
+  </si>
+  <si>
+    <t>Average (Jan 2016 -Feb 2021)</t>
+  </si>
+  <si>
+    <t>Reference: ge.vw_sales_products_fact</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
 </sst>
 </file>
 
@@ -301,7 +307,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="mmm\ yyyy"/>
-    <numFmt numFmtId="175" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -609,16 +615,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -657,27 +661,25 @@
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
@@ -685,14 +687,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -704,21 +705,66 @@
     <xf numFmtId="14" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="21">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="1"/>
+          <bgColor rgb="FF455A75"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="mmm\ yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="mmm\ yyyy"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -740,12 +786,7 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF455A75"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
     </dxf>
     <dxf>
       <fill>
@@ -756,39 +797,18 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="1"/>
+          <fgColor indexed="64"/>
           <bgColor rgb="FF455A75"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="1"/>
-        </left>
-        <right style="thin">
-          <color theme="1"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
@@ -863,16 +883,39 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="1"/>
+          <bgColor rgb="FF455A75"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="1"/>
+        </left>
+        <right style="thin">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4594,20 +4637,34 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{98625BD1-E203-4077-BF2F-554E3DB22AE4}" name="Table4" displayName="Table4" ref="A4:G66" totalsRowShown="0" headerRowDxfId="3" tableBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{262F8A15-1D2D-4EAA-B7DC-B57CFDC61180}" name="Table5" displayName="Table5" ref="A26:E62" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A26:E62" xr:uid="{262F8A15-1D2D-4EAA-B7DC-B57CFDC61180}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{D12618E9-FD0B-4951-A655-464A234706DD}" name="Timeline" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{DA9F4D9B-5179-4149-B6D7-31CC3A920507}" name="Values (USD)" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{EC43E806-A72F-4E66-9487-880ED83CBFA6}" name="Forecast (USD)" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{35C67A7E-0925-420D-A1E5-ED917E721E75}" name="Lower Bound (USD)" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{5A6ED3C3-9E03-499A-94FD-F56FB8822347}" name="Upper Bound (USD)" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{98625BD1-E203-4077-BF2F-554E3DB22AE4}" name="Table4" displayName="Table4" ref="A4:G66" totalsRowShown="0" headerRowDxfId="20" tableBorderDxfId="19">
   <autoFilter ref="A4:G66" xr:uid="{98625BD1-E203-4077-BF2F-554E3DB22AE4}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{D1DF04C4-4D31-437D-817B-68AFF82288EE}" name="Month" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{3C8EE0A6-2868-485B-8532-CDE2E530F4C3}" name="Revenue" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{129A6302-D0AC-4060-9634-375D014ECE7A}" name="Month Number" dataDxfId="7">
+    <tableColumn id="1" xr3:uid="{D1DF04C4-4D31-437D-817B-68AFF82288EE}" name="Month" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{3C8EE0A6-2868-485B-8532-CDE2E530F4C3}" name="Revenue" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{129A6302-D0AC-4060-9634-375D014ECE7A}" name="Month Number" dataDxfId="16">
       <calculatedColumnFormula>MONTH(A5)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{FBF68C6F-D035-4623-9D26-7402AA81EFE0}" name="Centered 12-Month Average"/>
-    <tableColumn id="5" xr3:uid="{152C23B2-CEC2-4570-864E-F8A152D81F82}" name="Percentage" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{D7EFD608-62C2-4398-B5FF-BA778A234819}" name="Seasonal Index" dataDxfId="5">
+    <tableColumn id="5" xr3:uid="{152C23B2-CEC2-4570-864E-F8A152D81F82}" name="Percentage" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{D7EFD608-62C2-4398-B5FF-BA778A234819}" name="Seasonal Index" dataDxfId="14">
       <calculatedColumnFormula>INDEX($O$8:$O$19, C5)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{D52B12B6-8EC1-4978-9F14-94ED4B0E21EE}" name="Deseasonalized_x000a_Revenue" dataDxfId="4">
+    <tableColumn id="7" xr3:uid="{D52B12B6-8EC1-4978-9F14-94ED4B0E21EE}" name="Deseasonalized_x000a_Revenue" dataDxfId="13">
       <calculatedColumnFormula>B5/F5</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4615,8 +4672,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{9CF8690E-B6DC-486F-B987-5473C2758BDE}" name="Table2" displayName="Table2" ref="A4:E78" totalsRowShown="0" headerRowDxfId="2">
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{9CF8690E-B6DC-486F-B987-5473C2758BDE}" name="Table2" displayName="Table2" ref="A4:E78" totalsRowShown="0" headerRowDxfId="12">
   <autoFilter ref="A4:E78" xr:uid="{9CF8690E-B6DC-486F-B987-5473C2758BDE}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{07F89375-7190-4B05-B2E7-DE1B971351A5}" name="Timeline"/>
@@ -4624,10 +4681,10 @@
     <tableColumn id="3" xr3:uid="{E9C17AD5-590F-466A-8EC8-B1E71DE83DB7}" name="Forecast">
       <calculatedColumnFormula>_xlfn.FORECAST.ETS(A5,$B$5:$B$66,$A$5:$A$66,1,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{6B09EB63-06E4-445F-AFED-AF1645AA0598}" name="Lower Confidence Bound" dataDxfId="13">
+    <tableColumn id="4" xr3:uid="{6B09EB63-06E4-445F-AFED-AF1645AA0598}" name="Lower Confidence Bound" dataDxfId="11">
       <calculatedColumnFormula>C5-_xlfn.FORECAST.ETS.CONFINT(A5,$B$5:$B$66,$A$5:$A$66,0.95,1,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7FAC777B-A5A3-4996-AEE4-54AF66F46DBF}" name="Upper Confidence Bound" dataDxfId="12">
+    <tableColumn id="5" xr3:uid="{7FAC777B-A5A3-4996-AEE4-54AF66F46DBF}" name="Upper Confidence Bound" dataDxfId="10">
       <calculatedColumnFormula>C5+_xlfn.FORECAST.ETS.CONFINT(A5,$B$5:$B$66,$A$5:$A$66,0.95,1,1)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4635,22 +4692,22 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{57841A73-03DE-45D1-8C59-39CEEF7D359B}" name="Table3" displayName="Table3" ref="G4:H11" totalsRowShown="0" headerRowDxfId="1">
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{57841A73-03DE-45D1-8C59-39CEEF7D359B}" name="Table3" displayName="Table3" ref="G4:H11" totalsRowShown="0" headerRowDxfId="9">
   <autoFilter ref="G4:H11" xr:uid="{57841A73-03DE-45D1-8C59-39CEEF7D359B}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{10EDEA80-2C97-4998-B9C9-D4FC160AEE46}" name="Statistic"/>
-    <tableColumn id="2" xr3:uid="{790D705A-39CD-4D78-90E4-DB2533C76A1E}" name="Value" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{790D705A-39CD-4D78-90E4-DB2533C76A1E}" name="Value" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{225E2087-5CF5-49EC-9441-65F181B8FF9B}" name="ge_vw_revenue_forecast" displayName="ge_vw_revenue_forecast" ref="A4:E66" tableType="queryTable" totalsRowShown="0" headerRowDxfId="0">
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{225E2087-5CF5-49EC-9441-65F181B8FF9B}" name="ge_vw_revenue_forecast" displayName="ge_vw_revenue_forecast" ref="A4:E66" tableType="queryTable" totalsRowShown="0" headerRowDxfId="7">
   <autoFilter ref="A4:E66" xr:uid="{225E2087-5CF5-49EC-9441-65F181B8FF9B}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{E781F119-C731-4E7B-BC62-3B41F93E0CAE}" uniqueName="1" name="Month" queryTableFieldId="1" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{E781F119-C731-4E7B-BC62-3B41F93E0CAE}" uniqueName="1" name="Month" queryTableFieldId="1" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{E84DB9B6-BA93-45AB-AE23-F4195DF62EED}" uniqueName="2" name="Series" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{8BD5E340-FA79-4A58-8558-47191851C90B}" uniqueName="3" name="Revenue" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{27DAE10F-D85A-4445-9D2F-C73AE24B1E72}" uniqueName="4" name="MoM_Change_USD" queryTableFieldId="4"/>
@@ -4961,1086 +5018,1017 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="12.77734375" customWidth="1"/>
-    <col min="5" max="5" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.77734375" customWidth="1"/>
+    <col min="3" max="3" width="15.21875" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" customWidth="1"/>
+    <col min="5" max="5" width="19.44140625" customWidth="1"/>
     <col min="6" max="6" width="13.44140625" customWidth="1"/>
     <col min="7" max="7" width="16.77734375" customWidth="1"/>
     <col min="8" max="8" width="12.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="11" t="s">
-        <v>67</v>
+      <c r="A1" s="9" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C3">
         <v>0.03</v>
       </c>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27" t="s">
-        <v>52</v>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C4">
         <v>-0.02</v>
       </c>
-      <c r="E4" s="27" t="s">
-        <v>52</v>
+      <c r="E4" s="25" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
-      <c r="E5" s="27" t="s">
-        <v>52</v>
+      <c r="E5" s="25" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="7">
+        <v>57</v>
+      </c>
+      <c r="C6" s="6">
         <f>Seasonality!M22</f>
         <v>381339.14068980265</v>
       </c>
-      <c r="E6" s="27" t="s">
-        <v>62</v>
+      <c r="E6" s="25" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="40" t="s">
+      <c r="A8" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="41" t="s">
+      <c r="B8" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="41" t="s">
-        <v>63</v>
-      </c>
-      <c r="E8" s="41" t="s">
-        <v>64</v>
-      </c>
-      <c r="F8" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="G8" s="41" t="s">
-        <v>54</v>
-      </c>
-      <c r="H8" s="41" t="s">
-        <v>55</v>
+      <c r="D8" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" s="37" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="31">
+      <c r="A9" s="29">
         <v>44256</v>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="30">
         <v>1</v>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="5">
         <f>INDEX(Seasonality!$O$8:$O$19,MONTH(Forecast!A9))</f>
         <v>0.55770217908347586</v>
       </c>
-      <c r="D9" s="34">
+      <c r="D9" s="31">
         <f>C9*$C$6*(1+$C$4)^B9</f>
         <v>208420.19633787265</v>
       </c>
-      <c r="E9" s="34">
+      <c r="E9" s="31">
         <f>C9*$C$6*(1+$C$5)^B9</f>
         <v>212673.66973252312</v>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="31">
         <f>C9*$C$6*(1+$C$3)^B9</f>
         <v>219053.87982449881</v>
       </c>
-      <c r="G9" s="34">
+      <c r="G9" s="31">
         <f>'Forecast Sheet'!C82</f>
         <v>763877.36900118995</v>
       </c>
-      <c r="H9" s="34">
+      <c r="H9" s="31">
         <f>E9-G9</f>
         <v>-551203.69926866679</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="31">
+      <c r="A10" s="29">
         <v>44287</v>
       </c>
-      <c r="B10" s="32">
+      <c r="B10" s="30">
         <f>B9+1</f>
         <v>2</v>
       </c>
-      <c r="C10" s="33">
+      <c r="C10" s="5">
         <f>INDEX(Seasonality!$O$8:$O$19,MONTH(Forecast!A10))</f>
         <v>9.3836861920854581E-2</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="31">
         <f t="shared" ref="D10:D20" si="0">C10*$C$6*(1+$C$4)^B10</f>
         <v>34366.635025645264</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="31">
         <f t="shared" ref="E10:E20" si="1">C10*$C$6*(1+$C$5)^B10</f>
         <v>35783.668289926347</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="31">
         <f t="shared" ref="F10:F20" si="2">C10*$C$6*(1+$C$3)^B10</f>
         <v>37962.89368878286</v>
       </c>
-      <c r="G10" s="34">
+      <c r="G10" s="31">
         <f>'Forecast Sheet'!C83</f>
         <v>769844.00126605912</v>
       </c>
-      <c r="H10" s="34">
+      <c r="H10" s="31">
         <f t="shared" ref="H10:H20" si="3">E10-G10</f>
         <v>-734060.33297613275</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="31">
+      <c r="A11" s="29">
         <v>44317</v>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="30">
         <f t="shared" ref="B11:B20" si="4">B10+1</f>
         <v>3</v>
       </c>
-      <c r="C11" s="33">
+      <c r="C11" s="5">
         <f>INDEX(Seasonality!$O$8:$O$19,MONTH(Forecast!A11))</f>
         <v>1.0827928889207721</v>
       </c>
-      <c r="D11" s="34">
+      <c r="D11" s="31">
         <f t="shared" si="0"/>
         <v>388628.82149900042</v>
       </c>
-      <c r="E11" s="34">
+      <c r="E11" s="31">
         <f t="shared" si="1"/>
         <v>412911.30980607617</v>
       </c>
-      <c r="F11" s="34">
+      <c r="F11" s="31">
         <f t="shared" si="2"/>
         <v>451199.33683046419</v>
       </c>
-      <c r="G11" s="34">
+      <c r="G11" s="31">
         <f>'Forecast Sheet'!C84</f>
         <v>775810.63353092759</v>
       </c>
-      <c r="H11" s="34">
+      <c r="H11" s="31">
         <f t="shared" si="3"/>
         <v>-362899.32372485142</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="31">
+      <c r="A12" s="29">
         <v>44348</v>
       </c>
-      <c r="B12" s="32">
+      <c r="B12" s="30">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="C12" s="33">
+      <c r="C12" s="5">
         <f>INDEX(Seasonality!$O$8:$O$19,MONTH(Forecast!A12))</f>
         <v>0.97911466482353871</v>
       </c>
-      <c r="D12" s="34">
+      <c r="D12" s="31">
         <f t="shared" si="0"/>
         <v>344388.97646287613</v>
       </c>
-      <c r="E12" s="34">
+      <c r="E12" s="31">
         <f t="shared" si="1"/>
         <v>373374.74492059241</v>
       </c>
-      <c r="F12" s="34">
+      <c r="F12" s="31">
         <f t="shared" si="2"/>
         <v>420236.56483962946</v>
       </c>
-      <c r="G12" s="34">
+      <c r="G12" s="31">
         <f>'Forecast Sheet'!C85</f>
         <v>781777.26579579676</v>
       </c>
-      <c r="H12" s="34">
+      <c r="H12" s="31">
         <f t="shared" si="3"/>
         <v>-408402.52087520435</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="31">
+      <c r="A13" s="29">
         <v>44378</v>
       </c>
-      <c r="B13" s="32">
+      <c r="B13" s="30">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="C13" s="33">
+      <c r="C13" s="5">
         <f>INDEX(Seasonality!$O$8:$O$19,MONTH(Forecast!A13))</f>
         <v>0.85333255083444914</v>
       </c>
-      <c r="D13" s="34">
+      <c r="D13" s="31">
         <f t="shared" si="0"/>
         <v>294144.05445653247</v>
       </c>
-      <c r="E13" s="34">
+      <c r="E13" s="31">
         <f t="shared" si="1"/>
         <v>325409.10165784619</v>
       </c>
-      <c r="F13" s="34">
+      <c r="F13" s="31">
         <f t="shared" si="2"/>
         <v>377238.33509319421</v>
       </c>
-      <c r="G13" s="34">
+      <c r="G13" s="31">
         <f>'Forecast Sheet'!C86</f>
         <v>787743.89806066535</v>
       </c>
-      <c r="H13" s="34">
+      <c r="H13" s="31">
         <f t="shared" si="3"/>
         <v>-462334.79640281916</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="31">
+      <c r="A14" s="29">
         <v>44409</v>
       </c>
-      <c r="B14" s="32">
+      <c r="B14" s="30">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="5">
         <f>INDEX(Seasonality!$O$8:$O$19,MONTH(Forecast!A14))</f>
         <v>0.91092864509183669</v>
       </c>
-      <c r="D14" s="34">
+      <c r="D14" s="31">
         <f t="shared" si="0"/>
         <v>307717.50102744321</v>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="31">
         <f t="shared" si="1"/>
         <v>347372.74674904719</v>
       </c>
-      <c r="F14" s="34">
+      <c r="F14" s="31">
         <f t="shared" si="2"/>
         <v>414781.22600728646</v>
       </c>
-      <c r="G14" s="34">
+      <c r="G14" s="31">
         <f>'Forecast Sheet'!C87</f>
         <v>793710.53032553452</v>
       </c>
-      <c r="H14" s="34">
+      <c r="H14" s="31">
         <f t="shared" si="3"/>
         <v>-446337.78357648733</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="31">
+      <c r="A15" s="29">
         <v>44440</v>
       </c>
-      <c r="B15" s="32">
+      <c r="B15" s="30">
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="C15" s="33">
+      <c r="C15" s="5">
         <f>INDEX(Seasonality!$O$8:$O$19,MONTH(Forecast!A15))</f>
         <v>0.98927759250581693</v>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="31">
         <f t="shared" si="0"/>
         <v>327500.58923275163</v>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="31">
         <f t="shared" si="1"/>
         <v>377250.26702984498</v>
       </c>
-      <c r="F15" s="34">
+      <c r="F15" s="31">
         <f t="shared" si="2"/>
         <v>463970.24414455984</v>
       </c>
-      <c r="G15" s="34">
+      <c r="G15" s="31">
         <f>'Forecast Sheet'!C88</f>
         <v>799677.16259040323</v>
       </c>
-      <c r="H15" s="34">
+      <c r="H15" s="31">
         <f t="shared" si="3"/>
         <v>-422426.89556055825</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="31">
+      <c r="A16" s="29">
         <v>44470</v>
       </c>
-      <c r="B16" s="32">
+      <c r="B16" s="30">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="C16" s="33">
+      <c r="C16" s="5">
         <f>INDEX(Seasonality!$O$8:$O$19,MONTH(Forecast!A16))</f>
         <v>1.0049429687230065</v>
       </c>
-      <c r="D16" s="34">
+      <c r="D16" s="31">
         <f t="shared" si="0"/>
         <v>326032.8835479581</v>
       </c>
-      <c r="E16" s="34">
+      <c r="E16" s="31">
         <f t="shared" si="1"/>
         <v>383224.08813509048</v>
       </c>
-      <c r="F16" s="34">
+      <c r="F16" s="31">
         <f t="shared" si="2"/>
         <v>485456.80931658344</v>
       </c>
-      <c r="G16" s="34">
+      <c r="G16" s="31">
         <f>'Forecast Sheet'!C89</f>
         <v>805643.79485527228</v>
       </c>
-      <c r="H16" s="34">
+      <c r="H16" s="31">
         <f t="shared" si="3"/>
         <v>-422419.7067201818</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="31">
+      <c r="A17" s="29">
         <v>44501</v>
       </c>
-      <c r="B17" s="32">
+      <c r="B17" s="30">
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="C17" s="33">
+      <c r="C17" s="5">
         <f>INDEX(Seasonality!$O$8:$O$19,MONTH(Forecast!A17))</f>
         <v>1.0813119968257763</v>
       </c>
-      <c r="D17" s="34">
+      <c r="D17" s="31">
         <f t="shared" si="0"/>
         <v>343793.04470613657</v>
       </c>
-      <c r="E17" s="34">
+      <c r="E17" s="31">
         <f t="shared" si="1"/>
         <v>412346.58768711612</v>
       </c>
-      <c r="F17" s="34">
+      <c r="F17" s="31">
         <f t="shared" si="2"/>
         <v>538018.77005764318</v>
       </c>
-      <c r="G17" s="34">
+      <c r="G17" s="31">
         <f>'Forecast Sheet'!C90</f>
         <v>811610.42712014087</v>
       </c>
-      <c r="H17" s="34">
+      <c r="H17" s="31">
         <f t="shared" si="3"/>
         <v>-399263.83943302475</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="31">
+      <c r="A18" s="29">
         <v>44531</v>
       </c>
-      <c r="B18" s="32">
+      <c r="B18" s="30">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="C18" s="33">
+      <c r="C18" s="5">
         <f>INDEX(Seasonality!$O$8:$O$19,MONTH(Forecast!A18))</f>
         <v>1.6935272993299522</v>
       </c>
-      <c r="D18" s="34">
+      <c r="D18" s="31">
         <f t="shared" si="0"/>
         <v>527672.3555032803</v>
       </c>
-      <c r="E18" s="34">
+      <c r="E18" s="31">
         <f t="shared" si="1"/>
         <v>645808.24506120617</v>
       </c>
-      <c r="F18" s="34">
+      <c r="F18" s="31">
         <f t="shared" si="2"/>
         <v>867912.27845323749</v>
       </c>
-      <c r="G18" s="34">
+      <c r="G18" s="31">
         <f>'Forecast Sheet'!C91</f>
         <v>817577.05938501004</v>
       </c>
-      <c r="H18" s="34">
+      <c r="H18" s="31">
         <f t="shared" si="3"/>
         <v>-171768.81432380388</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="31">
+      <c r="A19" s="29">
         <v>44562</v>
       </c>
-      <c r="B19" s="32">
+      <c r="B19" s="30">
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="C19" s="33">
+      <c r="C19" s="5">
         <f>INDEX(Seasonality!$O$8:$O$19,MONTH(Forecast!A19))</f>
         <v>1.2634175614796064</v>
       </c>
-      <c r="D19" s="34">
+      <c r="D19" s="31">
         <f t="shared" si="0"/>
         <v>385784.81167421717</v>
       </c>
-      <c r="E19" s="34">
+      <c r="E19" s="31">
         <f t="shared" si="1"/>
         <v>481790.56722703902</v>
       </c>
-      <c r="F19" s="34">
+      <c r="F19" s="31">
         <f t="shared" si="2"/>
         <v>666910.82175121037</v>
       </c>
-      <c r="G19" s="34">
+      <c r="G19" s="31">
         <f>'Forecast Sheet'!C92</f>
         <v>823543.69164987863</v>
       </c>
-      <c r="H19" s="34">
+      <c r="H19" s="31">
         <f t="shared" si="3"/>
         <v>-341753.12442283961</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="35">
+      <c r="A20" s="32">
         <v>44593</v>
       </c>
-      <c r="B20" s="36">
+      <c r="B20" s="33">
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="C20" s="22">
+      <c r="C20" s="20">
         <f>INDEX(Seasonality!$O$8:$O$19,MONTH(Forecast!A20))</f>
         <v>1.4898147904609165</v>
       </c>
-      <c r="D20" s="37">
+      <c r="D20" s="34">
         <f t="shared" si="0"/>
         <v>445816.94696442701</v>
       </c>
-      <c r="E20" s="37">
+      <c r="E20" s="34">
         <f t="shared" si="1"/>
         <v>568124.69198132423</v>
       </c>
-      <c r="F20" s="37">
+      <c r="F20" s="34">
         <f t="shared" si="2"/>
         <v>810009.96467850485</v>
       </c>
-      <c r="G20" s="37">
+      <c r="G20" s="34">
         <f>'Forecast Sheet'!C93</f>
         <v>829510.3239147478</v>
       </c>
-      <c r="H20" s="37">
+      <c r="H20" s="34">
         <f t="shared" si="3"/>
         <v>-261385.63193342357</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="43" t="s">
-        <v>66</v>
-      </c>
-      <c r="B21" s="44"/>
-      <c r="C21" s="44"/>
-      <c r="D21" s="45">
+      <c r="A21" s="39" t="s">
+        <v>62</v>
+      </c>
+      <c r="B21" s="40"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="41">
         <f>SUM(D9:D20)</f>
         <v>3934266.8164381408</v>
       </c>
-      <c r="E21" s="45">
+      <c r="E21" s="41">
         <f t="shared" ref="E21:F21" si="5">SUM(E9:E20)</f>
         <v>4576069.688277632</v>
       </c>
-      <c r="F21" s="45">
+      <c r="F21" s="41">
         <f t="shared" si="5"/>
         <v>5752751.1246855957</v>
       </c>
-      <c r="G21" s="45">
+      <c r="G21" s="41">
         <f>SUM(G9:G20)</f>
         <v>9560326.1574956253</v>
       </c>
-      <c r="H21" s="45">
+      <c r="H21" s="41">
         <f t="shared" ref="H21" si="6">SUM(H9:H20)</f>
         <v>-4984256.4692179952</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="28" t="s">
-        <v>68</v>
+      <c r="A25" s="26" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="40" t="s">
+      <c r="A26" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="B26" s="40" t="s">
-        <v>69</v>
-      </c>
-      <c r="C26" s="46" t="s">
-        <v>64</v>
-      </c>
-      <c r="D26" s="46" t="s">
-        <v>63</v>
-      </c>
-      <c r="E26" s="46" t="s">
+      <c r="B26" s="36" t="s">
         <v>65</v>
       </c>
+      <c r="C26" s="42" t="s">
+        <v>60</v>
+      </c>
+      <c r="D26" s="42" t="s">
+        <v>59</v>
+      </c>
+      <c r="E26" s="42" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="47">
+      <c r="A27" s="13">
         <f>Data!A43</f>
         <v>43525</v>
       </c>
-      <c r="B27" s="34">
+      <c r="B27" s="31">
         <f>Data!C43</f>
         <v>845925.09</v>
       </c>
-      <c r="C27" s="39"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="39"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="47">
+      <c r="A28" s="13">
         <f>Data!A44</f>
         <v>43556</v>
       </c>
-      <c r="B28" s="34">
+      <c r="B28" s="31">
         <f>Data!C44</f>
         <v>149892.71</v>
       </c>
-      <c r="C28" s="39"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="39"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="47">
+      <c r="A29" s="13">
         <f>Data!A45</f>
         <v>43586</v>
       </c>
-      <c r="B29" s="34">
+      <c r="B29" s="31">
         <f>Data!C45</f>
         <v>1594446.47</v>
       </c>
-      <c r="C29" s="39"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="39"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="47">
+      <c r="A30" s="13">
         <f>Data!A46</f>
         <v>43617</v>
       </c>
-      <c r="B30" s="34">
+      <c r="B30" s="31">
         <f>Data!C46</f>
         <v>1404861.4</v>
       </c>
-      <c r="C30" s="39"/>
-      <c r="D30" s="39"/>
-      <c r="E30" s="39"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="47">
+      <c r="A31" s="13">
         <f>Data!A47</f>
         <v>43647</v>
       </c>
-      <c r="B31" s="34">
+      <c r="B31" s="31">
         <f>Data!C47</f>
         <v>1408714.62</v>
       </c>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="47">
+      <c r="A32" s="13">
         <f>Data!A48</f>
         <v>43678</v>
       </c>
-      <c r="B32" s="34">
+      <c r="B32" s="31">
         <f>Data!C48</f>
         <v>1500784.77</v>
       </c>
-      <c r="C32" s="39"/>
-      <c r="D32" s="39"/>
-      <c r="E32" s="39"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="47">
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="13">
         <f>Data!A49</f>
         <v>43709</v>
       </c>
-      <c r="B33" s="34">
+      <c r="B33" s="31">
         <f>Data!C49</f>
         <v>1547870.73</v>
       </c>
-      <c r="C33" s="39"/>
-      <c r="D33" s="39"/>
-      <c r="E33" s="39"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="47">
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="13">
         <f>Data!A50</f>
         <v>43739</v>
       </c>
-      <c r="B34" s="34">
+      <c r="B34" s="31">
         <f>Data!C50</f>
         <v>1575168.82</v>
       </c>
-      <c r="C34" s="39"/>
-      <c r="D34" s="39"/>
-      <c r="E34" s="39"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="47">
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="13">
         <f>Data!A51</f>
         <v>43770</v>
       </c>
-      <c r="B35" s="34">
+      <c r="B35" s="31">
         <f>Data!C51</f>
         <v>1715659.88</v>
       </c>
-      <c r="C35" s="39"/>
-      <c r="D35" s="39"/>
-      <c r="E35" s="39"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="47">
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="13">
         <f>Data!A52</f>
         <v>43800</v>
       </c>
-      <c r="B36" s="34">
+      <c r="B36" s="31">
         <f>Data!C52</f>
         <v>2477295.85</v>
       </c>
-      <c r="C36" s="39"/>
-      <c r="D36" s="39"/>
-      <c r="E36" s="39"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="47">
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="13">
         <f>Data!A53</f>
         <v>43831</v>
       </c>
-      <c r="B37" s="34">
+      <c r="B37" s="31">
         <f>Data!C53</f>
         <v>2068951.12</v>
       </c>
-      <c r="C37" s="39"/>
-      <c r="D37" s="39"/>
-      <c r="E37" s="39"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="47">
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="13">
         <f>Data!A54</f>
         <v>43862</v>
       </c>
-      <c r="B38" s="34">
+      <c r="B38" s="31">
         <f>Data!C54</f>
         <v>2227379.5699999998</v>
       </c>
-      <c r="C38" s="39"/>
-      <c r="D38" s="39"/>
-      <c r="E38" s="39"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="47">
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="13">
         <f>Data!A55</f>
         <v>43891</v>
       </c>
-      <c r="B39" s="34">
+      <c r="B39" s="31">
         <f>Data!C55</f>
         <v>674990.66</v>
       </c>
-      <c r="C39" s="39"/>
-      <c r="D39" s="39"/>
-      <c r="E39" s="39"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="47">
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="13">
         <f>Data!A56</f>
         <v>43922</v>
       </c>
-      <c r="B40" s="34">
+      <c r="B40" s="31">
         <f>Data!C56</f>
         <v>217642.1</v>
       </c>
-      <c r="C40" s="39"/>
-      <c r="D40" s="39"/>
-      <c r="E40" s="39"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="47">
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="13">
         <f>Data!A57</f>
         <v>43952</v>
       </c>
-      <c r="B41" s="34">
+      <c r="B41" s="31">
         <f>Data!C57</f>
         <v>878026.63</v>
       </c>
-      <c r="C41" s="39"/>
-      <c r="D41" s="39"/>
-      <c r="E41" s="39"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="47">
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="13">
         <f>Data!A58</f>
         <v>43983</v>
       </c>
-      <c r="B42" s="34">
+      <c r="B42" s="31">
         <f>Data!C58</f>
         <v>763883.23</v>
       </c>
-      <c r="C42" s="39"/>
-      <c r="D42" s="39"/>
-      <c r="E42" s="39"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="47">
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="13">
         <f>Data!A59</f>
         <v>44013</v>
       </c>
-      <c r="B43" s="34">
+      <c r="B43" s="31">
         <f>Data!C59</f>
         <v>512805.18</v>
       </c>
-      <c r="C43" s="39"/>
-      <c r="D43" s="39"/>
-      <c r="E43" s="39"/>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="47">
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="13">
         <f>Data!A60</f>
         <v>44044</v>
       </c>
-      <c r="B44" s="34">
+      <c r="B44" s="31">
         <f>Data!C60</f>
         <v>416647.08</v>
       </c>
-      <c r="C44" s="39"/>
-      <c r="D44" s="39"/>
-      <c r="E44" s="39"/>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="47">
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="13">
         <f>Data!A61</f>
         <v>44075</v>
       </c>
-      <c r="B45" s="34">
+      <c r="B45" s="31">
         <f>Data!C61</f>
         <v>380431.52</v>
       </c>
-      <c r="C45" s="39"/>
-      <c r="D45" s="39"/>
-      <c r="E45" s="39"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="47">
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="13">
         <f>Data!A62</f>
         <v>44105</v>
       </c>
-      <c r="B46" s="34">
+      <c r="B46" s="31">
         <f>Data!C62</f>
         <v>245647.59</v>
       </c>
-      <c r="C46" s="39"/>
-      <c r="D46" s="39"/>
-      <c r="E46" s="39"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="47">
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="13">
         <f>Data!A63</f>
         <v>44136</v>
       </c>
-      <c r="B47" s="34">
+      <c r="B47" s="31">
         <f>Data!C63</f>
         <v>256701.02</v>
       </c>
-      <c r="C47" s="39"/>
-      <c r="D47" s="39"/>
-      <c r="E47" s="39"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="47">
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="13">
         <f>Data!A64</f>
         <v>44166</v>
       </c>
-      <c r="B48" s="34">
+      <c r="B48" s="31">
         <f>Data!C64</f>
         <v>651526.43999999994</v>
       </c>
-      <c r="C48" s="39"/>
-      <c r="D48" s="39"/>
-      <c r="E48" s="39"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="47">
+      <c r="A49" s="13">
         <f>Data!A65</f>
         <v>44197</v>
       </c>
-      <c r="B49" s="34">
+      <c r="B49" s="31">
         <f>Data!C65</f>
         <v>513021.58</v>
       </c>
-      <c r="C49" s="39"/>
-      <c r="D49" s="39"/>
-      <c r="E49" s="39"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="47">
+      <c r="A50" s="13">
         <f>Data!A66</f>
         <v>44228</v>
       </c>
-      <c r="B50" s="34">
+      <c r="B50" s="31">
         <f>Data!$C$66</f>
         <v>526266.9</v>
       </c>
-      <c r="C50" s="34">
+      <c r="C50" s="31">
         <f>Data!$C$66</f>
         <v>526266.9</v>
       </c>
-      <c r="D50" s="34">
+      <c r="D50" s="31">
         <f>Data!$C$66</f>
         <v>526266.9</v>
       </c>
-      <c r="E50" s="34">
+      <c r="E50" s="31">
         <f>Data!$C$66</f>
         <v>526266.9</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="47">
+      <c r="A51" s="13">
         <f>A9</f>
         <v>44256</v>
       </c>
-      <c r="B51" s="34"/>
-      <c r="C51" s="34">
+      <c r="B51" s="31"/>
+      <c r="C51" s="31">
         <f>E9</f>
         <v>212673.66973252312</v>
       </c>
-      <c r="D51" s="34">
+      <c r="D51" s="31">
         <f>D9</f>
         <v>208420.19633787265</v>
       </c>
-      <c r="E51" s="34">
+      <c r="E51" s="31">
         <f>F9</f>
         <v>219053.87982449881</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" s="47">
-        <f t="shared" ref="A52:A64" si="7">A10</f>
+      <c r="A52" s="13">
+        <f t="shared" ref="A52:A62" si="7">A10</f>
         <v>44287</v>
       </c>
-      <c r="B52" s="34"/>
-      <c r="C52" s="34">
+      <c r="B52" s="31"/>
+      <c r="C52" s="31">
         <f t="shared" ref="C52:C62" si="8">E10</f>
         <v>35783.668289926347</v>
       </c>
-      <c r="D52" s="34">
+      <c r="D52" s="31">
         <f t="shared" ref="D52:D62" si="9">D10</f>
         <v>34366.635025645264</v>
       </c>
-      <c r="E52" s="34">
+      <c r="E52" s="31">
         <f t="shared" ref="E52:E62" si="10">F10</f>
         <v>37962.89368878286</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53" s="47">
+      <c r="A53" s="13">
         <f t="shared" si="7"/>
         <v>44317</v>
       </c>
-      <c r="B53" s="34"/>
-      <c r="C53" s="34">
+      <c r="B53" s="31"/>
+      <c r="C53" s="31">
         <f t="shared" si="8"/>
         <v>412911.30980607617</v>
       </c>
-      <c r="D53" s="34">
+      <c r="D53" s="31">
         <f t="shared" si="9"/>
         <v>388628.82149900042</v>
       </c>
-      <c r="E53" s="34">
+      <c r="E53" s="31">
         <f t="shared" si="10"/>
         <v>451199.33683046419</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="47">
+      <c r="A54" s="13">
         <f t="shared" si="7"/>
         <v>44348</v>
       </c>
-      <c r="B54" s="34"/>
-      <c r="C54" s="34">
+      <c r="B54" s="31"/>
+      <c r="C54" s="31">
         <f t="shared" si="8"/>
         <v>373374.74492059241</v>
       </c>
-      <c r="D54" s="34">
+      <c r="D54" s="31">
         <f t="shared" si="9"/>
         <v>344388.97646287613</v>
       </c>
-      <c r="E54" s="34">
+      <c r="E54" s="31">
         <f t="shared" si="10"/>
         <v>420236.56483962946</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55" s="47">
+      <c r="A55" s="13">
         <f t="shared" si="7"/>
         <v>44378</v>
       </c>
-      <c r="B55" s="34"/>
-      <c r="C55" s="34">
+      <c r="B55" s="31"/>
+      <c r="C55" s="31">
         <f t="shared" si="8"/>
         <v>325409.10165784619</v>
       </c>
-      <c r="D55" s="34">
+      <c r="D55" s="31">
         <f t="shared" si="9"/>
         <v>294144.05445653247</v>
       </c>
-      <c r="E55" s="34">
+      <c r="E55" s="31">
         <f t="shared" si="10"/>
         <v>377238.33509319421</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" s="47">
+      <c r="A56" s="13">
         <f t="shared" si="7"/>
         <v>44409</v>
       </c>
-      <c r="B56" s="34"/>
-      <c r="C56" s="34">
+      <c r="B56" s="31"/>
+      <c r="C56" s="31">
         <f t="shared" si="8"/>
         <v>347372.74674904719</v>
       </c>
-      <c r="D56" s="34">
+      <c r="D56" s="31">
         <f t="shared" si="9"/>
         <v>307717.50102744321</v>
       </c>
-      <c r="E56" s="34">
+      <c r="E56" s="31">
         <f t="shared" si="10"/>
         <v>414781.22600728646</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" s="47">
+      <c r="A57" s="13">
         <f t="shared" si="7"/>
         <v>44440</v>
       </c>
-      <c r="B57" s="34"/>
-      <c r="C57" s="34">
+      <c r="B57" s="31"/>
+      <c r="C57" s="31">
         <f t="shared" si="8"/>
         <v>377250.26702984498</v>
       </c>
-      <c r="D57" s="34">
+      <c r="D57" s="31">
         <f t="shared" si="9"/>
         <v>327500.58923275163</v>
       </c>
-      <c r="E57" s="34">
+      <c r="E57" s="31">
         <f t="shared" si="10"/>
         <v>463970.24414455984</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" s="47">
+      <c r="A58" s="13">
         <f t="shared" si="7"/>
         <v>44470</v>
       </c>
-      <c r="B58" s="34"/>
-      <c r="C58" s="34">
+      <c r="B58" s="31"/>
+      <c r="C58" s="31">
         <f t="shared" si="8"/>
         <v>383224.08813509048</v>
       </c>
-      <c r="D58" s="34">
+      <c r="D58" s="31">
         <f t="shared" si="9"/>
         <v>326032.8835479581</v>
       </c>
-      <c r="E58" s="34">
+      <c r="E58" s="31">
         <f t="shared" si="10"/>
         <v>485456.80931658344</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59" s="47">
+      <c r="A59" s="13">
         <f t="shared" si="7"/>
         <v>44501</v>
       </c>
-      <c r="B59" s="34"/>
-      <c r="C59" s="34">
+      <c r="B59" s="31"/>
+      <c r="C59" s="31">
         <f t="shared" si="8"/>
         <v>412346.58768711612</v>
       </c>
-      <c r="D59" s="34">
+      <c r="D59" s="31">
         <f t="shared" si="9"/>
         <v>343793.04470613657</v>
       </c>
-      <c r="E59" s="34">
+      <c r="E59" s="31">
         <f t="shared" si="10"/>
         <v>538018.77005764318</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A60" s="47">
+      <c r="A60" s="13">
         <f>A18</f>
         <v>44531</v>
       </c>
-      <c r="B60" s="34"/>
-      <c r="C60" s="34">
+      <c r="B60" s="31"/>
+      <c r="C60" s="31">
         <f t="shared" si="8"/>
         <v>645808.24506120617</v>
       </c>
-      <c r="D60" s="34">
+      <c r="D60" s="31">
         <f t="shared" si="9"/>
         <v>527672.3555032803</v>
       </c>
-      <c r="E60" s="34">
+      <c r="E60" s="31">
         <f t="shared" si="10"/>
         <v>867912.27845323749</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" s="47">
+      <c r="A61" s="13">
         <f t="shared" si="7"/>
         <v>44562</v>
       </c>
-      <c r="B61" s="34"/>
-      <c r="C61" s="34">
+      <c r="B61" s="31"/>
+      <c r="C61" s="31">
         <f t="shared" si="8"/>
         <v>481790.56722703902</v>
       </c>
-      <c r="D61" s="34">
+      <c r="D61" s="31">
         <f t="shared" si="9"/>
         <v>385784.81167421717</v>
       </c>
-      <c r="E61" s="34">
+      <c r="E61" s="31">
         <f t="shared" si="10"/>
         <v>666910.82175121037</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A62" s="47">
+      <c r="A62" s="13">
         <f t="shared" si="7"/>
         <v>44593</v>
       </c>
-      <c r="B62" s="34"/>
-      <c r="C62" s="34">
+      <c r="B62" s="31"/>
+      <c r="C62" s="31">
         <f t="shared" si="8"/>
         <v>568124.69198132423</v>
       </c>
-      <c r="D62" s="34">
+      <c r="D62" s="31">
         <f t="shared" si="9"/>
         <v>445816.94696442701</v>
       </c>
-      <c r="E62" s="34">
+      <c r="E62" s="31">
         <f t="shared" si="10"/>
         <v>810009.96467850485</v>
       </c>
@@ -6054,6 +6042,9 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -6063,7 +6054,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>43</v>
       </c>
     </row>
@@ -6074,27 +6065,27 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -6116,15 +6107,15 @@
     <col min="7" max="7" width="14.77734375" customWidth="1"/>
     <col min="10" max="10" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5546875" style="13" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.77734375" style="12" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.77734375" style="10" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15.88671875" customWidth="1"/>
     <col min="16" max="16" width="13.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -6137,1956 +6128,1956 @@
       <c r="A3" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="15">
+      <c r="E3" s="13">
         <v>43647</v>
       </c>
       <c r="G3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="H3">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="50" t="s">
+      <c r="B4" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="41" t="s">
+      <c r="C4" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="41" t="s">
+      <c r="D4" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="E4" s="41" t="s">
+      <c r="E4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="41" t="s">
+      <c r="F4" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="G4" s="41" t="s">
+      <c r="G4" s="37" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5" s="48">
+      <c r="A5" s="43">
         <v>42370</v>
       </c>
-      <c r="B5" s="49">
+      <c r="B5" s="44">
         <v>649918.78</v>
       </c>
-      <c r="C5" s="49">
+      <c r="C5" s="44">
         <f>MONTH(A5)</f>
         <v>1</v>
       </c>
-      <c r="F5" s="6">
-        <f>INDEX($O$8:$O$19, C5)</f>
+      <c r="F5" s="5">
+        <f t="shared" ref="F5:F36" si="0">INDEX($O$8:$O$19, C5)</f>
         <v>1.2634175614796064</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="6">
         <f>B5/F5</f>
         <v>514413.28648215946</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="25">
+      <c r="A6" s="23">
         <v>42401</v>
       </c>
       <c r="B6" s="3">
         <v>891098.3</v>
       </c>
       <c r="C6" s="3">
-        <f t="shared" ref="C6:C66" si="0">MONTH(A6)</f>
+        <f t="shared" ref="C6:C66" si="1">MONTH(A6)</f>
         <v>2</v>
       </c>
-      <c r="F6" s="6">
-        <f>INDEX($O$8:$O$19, C6)</f>
+      <c r="F6" s="5">
+        <f t="shared" si="0"/>
         <v>1.4898147904609165</v>
       </c>
-      <c r="G6" s="7">
-        <f t="shared" ref="G6:G66" si="1">B6/F6</f>
+      <c r="G6" s="6">
+        <f t="shared" ref="G6:G66" si="2">B6/F6</f>
         <v>598126.89852831536</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="24">
+      <c r="A7" s="22">
         <v>42430</v>
       </c>
       <c r="B7" s="2">
         <v>338407.36</v>
       </c>
       <c r="C7" s="2">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="F7" s="5">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="F7" s="6">
-        <f>INDEX($O$8:$O$19, C7)</f>
         <v>0.55770217908347586</v>
       </c>
-      <c r="G7" s="7">
-        <f t="shared" si="1"/>
+      <c r="G7" s="6">
+        <f t="shared" si="2"/>
         <v>606788.66372036852</v>
       </c>
-      <c r="K7" s="51" t="s">
+      <c r="K7" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="L7" s="52" t="s">
+      <c r="L7" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="M7" s="52" t="s">
+      <c r="M7" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="N7" s="52" t="s">
+      <c r="N7" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="O7" s="53" t="s">
+      <c r="O7" s="48" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" s="25">
+      <c r="A8" s="23">
         <v>42461</v>
       </c>
       <c r="B8" s="3">
         <v>110591.63</v>
       </c>
       <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="F8" s="5">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="F8" s="6">
-        <f>INDEX($O$8:$O$19, C8)</f>
         <v>9.3836861920854581E-2</v>
       </c>
-      <c r="G8" s="7">
-        <f t="shared" si="1"/>
+      <c r="G8" s="6">
+        <f t="shared" si="2"/>
         <v>1178552.0928148364</v>
       </c>
-      <c r="K8" s="17">
+      <c r="K8" s="15">
         <v>1</v>
       </c>
-      <c r="L8" s="12" t="s">
+      <c r="L8" s="10" t="s">
         <v>23</v>
       </c>
       <c r="M8">
-        <f>COUNTIFS(C5:C66,K8,A5:A66,"&lt;=" &amp; $E$3, E5:E66, "&gt;0")</f>
+        <f t="shared" ref="M8:M19" si="3">COUNTIFS(C5:C66,K8,A5:A66,"&lt;=" &amp; $E$3, E5:E66, "&gt;0")</f>
         <v>3</v>
       </c>
-      <c r="N8" s="6">
-        <f>AVERAGEIFS(E5:E66,C5:C66,K8,A5:A66,"&lt;=" &amp; $E$3)</f>
+      <c r="N8" s="5">
+        <f t="shared" ref="N8:N19" si="4">AVERAGEIFS(E5:E66,C5:C66,K8,A5:A66,"&lt;=" &amp; $E$3)</f>
         <v>1.2551215376059621</v>
       </c>
-      <c r="O8" s="18">
-        <f>N8/AVERAGE($N$8:$N$19)</f>
+      <c r="O8" s="16">
+        <f t="shared" ref="O8:O19" si="5">N8/AVERAGE($N$8:$N$19)</f>
         <v>1.2634175614796064</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="24">
+      <c r="A9" s="22">
         <v>42491</v>
       </c>
       <c r="B9" s="2">
         <v>595986.18000000005</v>
       </c>
       <c r="C9" s="2">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="F9" s="5">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="F9" s="6">
-        <f>INDEX($O$8:$O$19, C9)</f>
         <v>1.0827928889207721</v>
       </c>
-      <c r="G9" s="7">
-        <f t="shared" si="1"/>
+      <c r="G9" s="6">
+        <f t="shared" si="2"/>
         <v>550415.67607081716</v>
       </c>
-      <c r="K9" s="17">
+      <c r="K9" s="15">
         <f>K8+1</f>
         <v>2</v>
       </c>
-      <c r="L9" s="12" t="s">
+      <c r="L9" s="10" t="s">
         <v>24</v>
       </c>
       <c r="M9">
-        <f>COUNTIFS(C6:C67,K9,A6:A67,"&lt;=" &amp; $E$3, E6:E67, "&gt;0")</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="N9" s="6">
-        <f>AVERAGEIFS(E6:E67,C6:C67,K9,A6:A67,"&lt;=" &amp; $E$3)</f>
+      <c r="N9" s="5">
+        <f t="shared" si="4"/>
         <v>1.4800321663738352</v>
       </c>
-      <c r="O9" s="18">
-        <f>N9/AVERAGE($N$8:$N$19)</f>
+      <c r="O9" s="16">
+        <f t="shared" si="5"/>
         <v>1.4898147904609165</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" s="25">
+      <c r="A10" s="23">
         <v>42522</v>
       </c>
       <c r="B10" s="3">
         <v>518585.28</v>
       </c>
       <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="F10" s="5">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="F10" s="6">
-        <f>INDEX($O$8:$O$19, C10)</f>
         <v>0.97911466482353871</v>
       </c>
-      <c r="G10" s="7">
-        <f t="shared" si="1"/>
+      <c r="G10" s="6">
+        <f t="shared" si="2"/>
         <v>529647.13800243428</v>
       </c>
-      <c r="K10" s="17">
-        <f t="shared" ref="K10:K17" si="2">K9+1</f>
+      <c r="K10" s="15">
+        <f t="shared" ref="K10:K17" si="6">K9+1</f>
         <v>3</v>
       </c>
-      <c r="L10" s="12" t="s">
+      <c r="L10" s="10" t="s">
         <v>25</v>
       </c>
       <c r="M10">
-        <f>COUNTIFS(C7:C68,K10,A7:A68,"&lt;=" &amp; $E$3, E7:E68, "&gt;0")</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="N10" s="6">
-        <f>AVERAGEIFS(E7:E68,C7:C68,K10,A7:A68,"&lt;=" &amp; $E$3)</f>
+      <c r="N10" s="5">
+        <f t="shared" si="4"/>
         <v>0.55404011933923625</v>
       </c>
-      <c r="O10" s="18">
-        <f>N10/AVERAGE($N$8:$N$19)</f>
+      <c r="O10" s="16">
+        <f t="shared" si="5"/>
         <v>0.55770217908347586</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="24">
+      <c r="A11" s="22">
         <v>42552</v>
       </c>
       <c r="B11" s="2">
         <v>454959.83</v>
       </c>
       <c r="C11" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="6">
         <f>(AVERAGE(B5:B16)+AVERAGE(B6:B17))/2</f>
         <v>579740.96416666661</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="6">
         <f>B11/D11</f>
         <v>0.78476398619505872</v>
       </c>
-      <c r="F11" s="6">
-        <f>INDEX($O$8:$O$19, C11)</f>
+      <c r="F11" s="5">
+        <f t="shared" si="0"/>
         <v>0.85333255083444914</v>
       </c>
-      <c r="G11" s="7">
-        <f t="shared" si="1"/>
+      <c r="G11" s="6">
+        <f t="shared" si="2"/>
         <v>533156.53968093451</v>
       </c>
-      <c r="K11" s="17">
-        <f t="shared" si="2"/>
+      <c r="K11" s="15">
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="L11" s="12" t="s">
+      <c r="L11" s="10" t="s">
         <v>26</v>
       </c>
       <c r="M11">
-        <f>COUNTIFS(C8:C69,K11,A8:A69,"&lt;=" &amp; $E$3, E8:E69, "&gt;0")</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="N11" s="6">
-        <f>AVERAGEIFS(E8:E69,C8:C69,K11,A8:A69,"&lt;=" &amp; $E$3)</f>
+      <c r="N11" s="5">
+        <f t="shared" si="4"/>
         <v>9.3220697581796644E-2</v>
       </c>
-      <c r="O11" s="18">
-        <f>N11/AVERAGE($N$8:$N$19)</f>
+      <c r="O11" s="16">
+        <f t="shared" si="5"/>
         <v>9.3836861920854581E-2</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="25">
+      <c r="A12" s="23">
         <v>42583</v>
       </c>
       <c r="B12" s="3">
         <v>547512.68999999994</v>
       </c>
       <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="D12" s="6">
+        <f t="shared" ref="D12:D60" si="7">(AVERAGE(B6:B17)+AVERAGE(B7:B18))/2</f>
+        <v>574725.29374999995</v>
+      </c>
+      <c r="E12" s="6">
+        <f t="shared" ref="E12:E60" si="8">B12/D12</f>
+        <v>0.95265111167729943</v>
+      </c>
+      <c r="F12" s="5">
         <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="D12" s="7">
-        <f t="shared" ref="D12:D60" si="3">(AVERAGE(B6:B17)+AVERAGE(B7:B18))/2</f>
-        <v>574725.29374999995</v>
-      </c>
-      <c r="E12" s="7">
-        <f t="shared" ref="E12:E60" si="4">B12/D12</f>
-        <v>0.95265111167729943</v>
-      </c>
-      <c r="F12" s="6">
-        <f>INDEX($O$8:$O$19, C12)</f>
         <v>0.91092864509183669</v>
       </c>
-      <c r="G12" s="7">
-        <f t="shared" si="1"/>
+      <c r="G12" s="6">
+        <f t="shared" si="2"/>
         <v>601048.93281163822</v>
       </c>
-      <c r="K12" s="17">
-        <f t="shared" si="2"/>
+      <c r="K12" s="15">
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L12" s="12" t="s">
+      <c r="L12" s="10" t="s">
         <v>27</v>
       </c>
       <c r="M12">
-        <f>COUNTIFS(C9:C70,K12,A9:A70,"&lt;=" &amp; $E$3, E9:E70, "&gt;0")</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="N12" s="6">
-        <f>AVERAGEIFS(E9:E70,C9:C70,K12,A9:A70,"&lt;=" &amp; $E$3)</f>
+      <c r="N12" s="5">
+        <f t="shared" si="4"/>
         <v>1.0756829072879548</v>
       </c>
-      <c r="O12" s="18">
-        <f>N12/AVERAGE($N$8:$N$19)</f>
+      <c r="O12" s="16">
+        <f t="shared" si="5"/>
         <v>1.0827928889207721</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="24">
+      <c r="A13" s="22">
         <v>42614</v>
       </c>
       <c r="B13" s="2">
         <v>567421.12</v>
       </c>
       <c r="C13" s="2">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="D13" s="6">
+        <f t="shared" si="7"/>
+        <v>568569.84041666659</v>
+      </c>
+      <c r="E13" s="6">
+        <f t="shared" si="8"/>
+        <v>0.99797963181475691</v>
+      </c>
+      <c r="F13" s="5">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="D13" s="7">
+        <v>0.98927759250581693</v>
+      </c>
+      <c r="G13" s="6">
+        <f t="shared" si="2"/>
+        <v>573571.18396135466</v>
+      </c>
+      <c r="K13" s="15">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="L13" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="M13">
         <f t="shared" si="3"/>
-        <v>568569.84041666659</v>
-      </c>
-      <c r="E13" s="7">
+        <v>3</v>
+      </c>
+      <c r="N13" s="5">
         <f t="shared" si="4"/>
-        <v>0.99797963181475691</v>
-      </c>
-      <c r="F13" s="6">
-        <f>INDEX($O$8:$O$19, C13)</f>
-        <v>0.98927759250581693</v>
-      </c>
-      <c r="G13" s="7">
-        <f t="shared" si="1"/>
-        <v>573571.18396135466</v>
-      </c>
-      <c r="K13" s="17">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-      <c r="L13" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="M13">
-        <f>COUNTIFS(C10:C71,K13,A10:A71,"&lt;=" &amp; $E$3, E10:E71, "&gt;0")</f>
-        <v>3</v>
-      </c>
-      <c r="N13" s="6">
-        <f>AVERAGEIFS(E10:E71,C10:C71,K13,A10:A71,"&lt;=" &amp; $E$3)</f>
         <v>0.97268546921785271</v>
       </c>
-      <c r="O13" s="18">
-        <f>N13/AVERAGE($N$8:$N$19)</f>
+      <c r="O13" s="16">
+        <f t="shared" si="5"/>
         <v>0.97911466482353871</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="25">
+      <c r="A14" s="23">
         <v>42644</v>
       </c>
       <c r="B14" s="3">
         <v>623959.56999999995</v>
       </c>
       <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="D14" s="6">
+        <f t="shared" si="7"/>
+        <v>566104.40999999992</v>
+      </c>
+      <c r="E14" s="6">
+        <f t="shared" si="8"/>
+        <v>1.1021987445743446</v>
+      </c>
+      <c r="F14" s="5">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="D14" s="7">
+        <v>1.0049429687230065</v>
+      </c>
+      <c r="G14" s="6">
+        <f t="shared" si="2"/>
+        <v>620890.52754194906</v>
+      </c>
+      <c r="K14" s="15">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="L14" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="M14">
         <f t="shared" si="3"/>
-        <v>566104.40999999992</v>
-      </c>
-      <c r="E14" s="7">
+        <v>4</v>
+      </c>
+      <c r="N14" s="5">
         <f t="shared" si="4"/>
-        <v>1.1021987445743446</v>
-      </c>
-      <c r="F14" s="6">
-        <f>INDEX($O$8:$O$19, C14)</f>
-        <v>1.0049429687230065</v>
-      </c>
-      <c r="G14" s="7">
-        <f t="shared" si="1"/>
-        <v>620890.52754194906</v>
-      </c>
-      <c r="K14" s="17">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-      <c r="L14" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="M14">
-        <f>COUNTIFS(C11:C72,K14,A11:A72,"&lt;=" &amp; $E$3, E11:E72, "&gt;0")</f>
-        <v>4</v>
-      </c>
-      <c r="N14" s="6">
-        <f>AVERAGEIFS(E11:E72,C11:C72,K14,A11:A72,"&lt;=" &amp; $E$3)</f>
         <v>0.84772928281782478</v>
       </c>
-      <c r="O14" s="18">
-        <f>N14/AVERAGE($N$8:$N$19)</f>
+      <c r="O14" s="16">
+        <f t="shared" si="5"/>
         <v>0.85333255083444914</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="24">
+      <c r="A15" s="22">
         <v>42675</v>
       </c>
       <c r="B15" s="2">
         <v>649949.36</v>
       </c>
       <c r="C15" s="2">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="D15" s="6">
+        <f t="shared" si="7"/>
+        <v>564781.96083333332</v>
+      </c>
+      <c r="E15" s="6">
+        <f t="shared" si="8"/>
+        <v>1.1507969536438496</v>
+      </c>
+      <c r="F15" s="5">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="D15" s="7">
+        <v>1.0813119968257763</v>
+      </c>
+      <c r="G15" s="6">
+        <f t="shared" si="2"/>
+        <v>601074.77019393642</v>
+      </c>
+      <c r="K15" s="15">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="L15" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M15">
         <f t="shared" si="3"/>
-        <v>564781.96083333332</v>
-      </c>
-      <c r="E15" s="7">
+        <v>3</v>
+      </c>
+      <c r="N15" s="5">
         <f t="shared" si="4"/>
-        <v>1.1507969536438496</v>
-      </c>
-      <c r="F15" s="6">
-        <f>INDEX($O$8:$O$19, C15)</f>
-        <v>1.0813119968257763</v>
-      </c>
-      <c r="G15" s="7">
-        <f t="shared" si="1"/>
-        <v>601074.77019393642</v>
-      </c>
-      <c r="K15" s="17">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="L15" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="M15">
-        <f>COUNTIFS(C12:C73,K15,A12:A73,"&lt;=" &amp; $E$3, E12:E73, "&gt;0")</f>
-        <v>3</v>
-      </c>
-      <c r="N15" s="6">
-        <f>AVERAGEIFS(E12:E73,C12:C73,K15,A12:A73,"&lt;=" &amp; $E$3)</f>
         <v>0.90494718178368228</v>
       </c>
-      <c r="O15" s="18">
-        <f>N15/AVERAGE($N$8:$N$19)</f>
+      <c r="O15" s="16">
+        <f t="shared" si="5"/>
         <v>0.91092864509183669</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="25">
+      <c r="A16" s="23">
         <v>42705</v>
       </c>
       <c r="B16" s="3">
         <v>998403.46</v>
       </c>
       <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="D16" s="6">
+        <f t="shared" si="7"/>
+        <v>570341.0774999999</v>
+      </c>
+      <c r="E16" s="6">
+        <f t="shared" si="8"/>
+        <v>1.7505375281337685</v>
+      </c>
+      <c r="F16" s="5">
         <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="D16" s="7">
-        <f t="shared" si="3"/>
-        <v>570341.0774999999</v>
-      </c>
-      <c r="E16" s="7">
-        <f t="shared" si="4"/>
-        <v>1.7505375281337685</v>
-      </c>
-      <c r="F16" s="6">
-        <f>INDEX($O$8:$O$19, C16)</f>
         <v>1.6935272993299522</v>
       </c>
-      <c r="G16" s="7">
-        <f t="shared" si="1"/>
+      <c r="G16" s="6">
+        <f t="shared" si="2"/>
         <v>589540.81247761438</v>
       </c>
-      <c r="K16" s="17">
+      <c r="K16" s="15">
         <f>K15+1</f>
         <v>9</v>
       </c>
-      <c r="L16" s="12" t="s">
+      <c r="L16" s="10" t="s">
         <v>31</v>
       </c>
       <c r="M16">
-        <f>COUNTIFS(C13:C74,K16,A13:A74,"&lt;=" &amp; $E$3, E13:E74, "&gt;0")</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="N16" s="6">
-        <f>AVERAGEIFS(E13:E74,C13:C74,K16,A13:A74,"&lt;=" &amp; $E$3)</f>
+      <c r="N16" s="5">
+        <f t="shared" si="4"/>
         <v>0.9827816637049871</v>
       </c>
-      <c r="O16" s="18">
-        <f>N16/AVERAGE($N$8:$N$19)</f>
+      <c r="O16" s="16">
+        <f t="shared" si="5"/>
         <v>0.98927759250581693</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="24">
+      <c r="A17" s="22">
         <v>42736</v>
       </c>
       <c r="B17" s="2">
         <v>670114.80000000005</v>
       </c>
       <c r="C17" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="D17" s="6">
+        <f t="shared" si="7"/>
+        <v>577423.28208333324</v>
+      </c>
+      <c r="E17" s="6">
+        <f t="shared" si="8"/>
+        <v>1.1605261180017499</v>
+      </c>
+      <c r="F17" s="5">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D17" s="7">
+        <v>1.2634175614796064</v>
+      </c>
+      <c r="G17" s="6">
+        <f t="shared" si="2"/>
+        <v>530398.51623972913</v>
+      </c>
+      <c r="K17" s="15">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="L17" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="M17">
         <f t="shared" si="3"/>
-        <v>577423.28208333324</v>
-      </c>
-      <c r="E17" s="7">
+        <v>3</v>
+      </c>
+      <c r="N17" s="5">
         <f t="shared" si="4"/>
-        <v>1.1605261180017499</v>
-      </c>
-      <c r="F17" s="6">
-        <f>INDEX($O$8:$O$19, C17)</f>
-        <v>1.2634175614796064</v>
-      </c>
-      <c r="G17" s="7">
-        <f t="shared" si="1"/>
-        <v>530398.51623972913</v>
-      </c>
-      <c r="K17" s="17">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="L17" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="M17">
-        <f>COUNTIFS(C14:C75,K17,A14:A75,"&lt;=" &amp; $E$3, E14:E75, "&gt;0")</f>
-        <v>3</v>
-      </c>
-      <c r="N17" s="6">
-        <f>AVERAGEIFS(E14:E75,C14:C75,K17,A14:A75,"&lt;=" &amp; $E$3)</f>
         <v>0.99834417580262536</v>
       </c>
-      <c r="O17" s="18">
-        <f>N17/AVERAGE($N$8:$N$19)</f>
+      <c r="O17" s="16">
+        <f t="shared" si="5"/>
         <v>1.0049429687230065</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" s="25">
+      <c r="A18" s="23">
         <v>42767</v>
       </c>
       <c r="B18" s="3">
         <v>750526.19</v>
       </c>
       <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="D18" s="6">
+        <f t="shared" si="7"/>
+        <v>581702.16749999998</v>
+      </c>
+      <c r="E18" s="6">
+        <f t="shared" si="8"/>
+        <v>1.2902241592558616</v>
+      </c>
+      <c r="F18" s="5">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="D18" s="7">
-        <f t="shared" si="3"/>
-        <v>581702.16749999998</v>
-      </c>
-      <c r="E18" s="7">
-        <f t="shared" si="4"/>
-        <v>1.2902241592558616</v>
-      </c>
-      <c r="F18" s="6">
-        <f>INDEX($O$8:$O$19, C18)</f>
         <v>1.4898147904609165</v>
       </c>
-      <c r="G18" s="7">
-        <f t="shared" si="1"/>
+      <c r="G18" s="6">
+        <f t="shared" si="2"/>
         <v>503771.47200143139</v>
       </c>
-      <c r="K18" s="17">
+      <c r="K18" s="15">
         <f>K17+1</f>
         <v>11</v>
       </c>
-      <c r="L18" s="12" t="s">
+      <c r="L18" s="10" t="s">
         <v>33</v>
       </c>
       <c r="M18">
-        <f>COUNTIFS(C15:C76,K18,A15:A76,"&lt;=" &amp; $E$3, E15:E76, "&gt;0")</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="N18" s="6">
-        <f>AVERAGEIFS(E15:E76,C15:C76,K18,A15:A76,"&lt;=" &amp; $E$3)</f>
+      <c r="N18" s="5">
+        <f t="shared" si="4"/>
         <v>1.074211739227632</v>
       </c>
-      <c r="O18" s="18">
-        <f>N18/AVERAGE($N$8:$N$19)</f>
+      <c r="O18" s="16">
+        <f t="shared" si="5"/>
         <v>1.0813119968257763</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="24">
+      <c r="A19" s="22">
         <v>42795</v>
       </c>
       <c r="B19" s="2">
         <v>331248.59000000003</v>
       </c>
       <c r="C19" s="2">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="D19" s="6">
+        <f t="shared" si="7"/>
+        <v>588569.68166666653</v>
+      </c>
+      <c r="E19" s="6">
+        <f t="shared" si="8"/>
+        <v>0.5628026728491955</v>
+      </c>
+      <c r="F19" s="5">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="D19" s="7">
-        <f t="shared" si="3"/>
-        <v>588569.68166666653</v>
-      </c>
-      <c r="E19" s="7">
-        <f t="shared" si="4"/>
-        <v>0.5628026728491955</v>
-      </c>
-      <c r="F19" s="6">
-        <f>INDEX($O$8:$O$19, C19)</f>
         <v>0.55770217908347586</v>
       </c>
-      <c r="G19" s="7">
-        <f t="shared" si="1"/>
+      <c r="G19" s="6">
+        <f t="shared" si="2"/>
         <v>593952.47575394413</v>
       </c>
-      <c r="K19" s="19">
+      <c r="K19" s="17">
         <f>K18+1</f>
         <v>12</v>
       </c>
-      <c r="L19" s="20" t="s">
+      <c r="L19" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="M19" s="21">
-        <f>COUNTIFS(C16:C77,K19,A16:A77,"&lt;=" &amp; $E$3, E16:E77, "&gt;0")</f>
+      <c r="M19" s="19">
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="N19" s="22">
-        <f>AVERAGEIFS(E16:E77,C16:C77,K19,A16:A77,"&lt;=" &amp; $E$3)</f>
+      <c r="N19" s="20">
+        <f t="shared" si="4"/>
         <v>1.6824070305175922</v>
       </c>
-      <c r="O19" s="23">
-        <f>N19/AVERAGE($N$8:$N$19)</f>
+      <c r="O19" s="21">
+        <f t="shared" si="5"/>
         <v>1.6935272993299522</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" s="25">
+      <c r="A20" s="23">
         <v>42826</v>
       </c>
       <c r="B20" s="3">
         <v>58580.07</v>
       </c>
       <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="D20" s="6">
+        <f t="shared" si="7"/>
+        <v>593716.17499999981</v>
+      </c>
+      <c r="E20" s="6">
+        <f t="shared" si="8"/>
+        <v>9.8666791417633209E-2</v>
+      </c>
+      <c r="F20" s="5">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="D20" s="7">
-        <f t="shared" si="3"/>
-        <v>593716.17499999981</v>
-      </c>
-      <c r="E20" s="7">
-        <f t="shared" si="4"/>
-        <v>9.8666791417633209E-2</v>
-      </c>
-      <c r="F20" s="6">
-        <f>INDEX($O$8:$O$19, C20)</f>
         <v>9.3836861920854581E-2</v>
       </c>
-      <c r="G20" s="7">
-        <f t="shared" si="1"/>
+      <c r="G20" s="6">
+        <f t="shared" si="2"/>
         <v>624275.6716375337</v>
       </c>
       <c r="J20" t="s">
         <v>39</v>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="14">
         <f>COUNT(K8:K19)</f>
         <v>12</v>
       </c>
-      <c r="L20" s="12"/>
+      <c r="L20" s="10"/>
       <c r="M20"/>
-      <c r="O20" s="6">
+      <c r="O20" s="5">
         <f>SUM(O8:O19)</f>
         <v>12.000000000000004</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" s="24">
+      <c r="A21" s="22">
         <v>42856</v>
       </c>
       <c r="B21" s="2">
         <v>616258.96</v>
       </c>
       <c r="C21" s="2">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="D21" s="6">
+        <f t="shared" si="7"/>
+        <v>594146.82041666657</v>
+      </c>
+      <c r="E21" s="6">
+        <f t="shared" si="8"/>
+        <v>1.0372166252910795</v>
+      </c>
+      <c r="F21" s="5">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="D21" s="7">
-        <f t="shared" si="3"/>
-        <v>594146.82041666657</v>
-      </c>
-      <c r="E21" s="7">
-        <f t="shared" si="4"/>
-        <v>1.0372166252910795</v>
-      </c>
-      <c r="F21" s="6">
-        <f>INDEX($O$8:$O$19, C21)</f>
         <v>1.0827928889207721</v>
       </c>
-      <c r="G21" s="7">
-        <f t="shared" si="1"/>
+      <c r="G21" s="6">
+        <f t="shared" si="2"/>
         <v>569138.35166966228</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" s="25">
+      <c r="A22" s="23">
         <v>42887</v>
       </c>
       <c r="B22" s="3">
         <v>631731.30000000005</v>
       </c>
       <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="D22" s="6">
+        <f t="shared" si="7"/>
+        <v>606419.62208333332</v>
+      </c>
+      <c r="E22" s="6">
+        <f t="shared" si="8"/>
+        <v>1.0417395430406908</v>
+      </c>
+      <c r="F22" s="5">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="D22" s="7">
-        <f t="shared" si="3"/>
-        <v>606419.62208333332</v>
-      </c>
-      <c r="E22" s="7">
-        <f t="shared" si="4"/>
-        <v>1.0417395430406908</v>
-      </c>
-      <c r="F22" s="6">
-        <f>INDEX($O$8:$O$19, C22)</f>
         <v>0.97911466482353871</v>
       </c>
-      <c r="G22" s="7">
-        <f t="shared" si="1"/>
+      <c r="G22" s="6">
+        <f t="shared" si="2"/>
         <v>645206.65729570505</v>
       </c>
-      <c r="K22" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="M22" s="29">
+      <c r="K22" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="M22" s="27">
         <f>AVERAGE(G64:G66)</f>
         <v>381339.14068980265</v>
       </c>
-      <c r="O22" s="27" t="s">
-        <v>74</v>
+      <c r="O22" s="25" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23" s="24">
+      <c r="A23" s="22">
         <v>42917</v>
       </c>
       <c r="B23" s="2">
         <v>511786.72</v>
       </c>
       <c r="C23" s="2">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="D23" s="6">
+        <f t="shared" si="7"/>
+        <v>628741.87875000003</v>
+      </c>
+      <c r="E23" s="6">
+        <f t="shared" si="8"/>
+        <v>0.81398541642793343</v>
+      </c>
+      <c r="F23" s="5">
         <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="D23" s="7">
-        <f t="shared" si="3"/>
-        <v>628741.87875000003</v>
-      </c>
-      <c r="E23" s="7">
-        <f t="shared" si="4"/>
-        <v>0.81398541642793343</v>
-      </c>
-      <c r="F23" s="6">
-        <f>INDEX($O$8:$O$19, C23)</f>
         <v>0.85333255083444914</v>
       </c>
-      <c r="G23" s="7">
-        <f t="shared" si="1"/>
+      <c r="G23" s="6">
+        <f t="shared" si="2"/>
         <v>599750.61246584181</v>
       </c>
-      <c r="K23" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="M23" s="30">
+      <c r="K23" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="M23" s="28">
         <v>44228</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A24" s="25">
+      <c r="A24" s="23">
         <v>42948</v>
       </c>
       <c r="B24" s="3">
         <v>593379.05000000005</v>
       </c>
       <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="D24" s="6">
+        <f t="shared" si="7"/>
+        <v>663774.25625000009</v>
+      </c>
+      <c r="E24" s="6">
+        <f t="shared" si="8"/>
+        <v>0.89394706771591514</v>
+      </c>
+      <c r="F24" s="5">
         <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="D24" s="7">
-        <f t="shared" si="3"/>
-        <v>663774.25625000009</v>
-      </c>
-      <c r="E24" s="7">
-        <f t="shared" si="4"/>
-        <v>0.89394706771591514</v>
-      </c>
-      <c r="F24" s="6">
-        <f>INDEX($O$8:$O$19, C24)</f>
         <v>0.91092864509183669</v>
       </c>
-      <c r="G24" s="7">
-        <f t="shared" si="1"/>
+      <c r="G24" s="6">
+        <f t="shared" si="2"/>
         <v>651400.14335609961</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" s="24">
+      <c r="A25" s="22">
         <v>42979</v>
       </c>
       <c r="B25" s="2">
         <v>686375.1</v>
       </c>
       <c r="C25" s="2">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="D25" s="6">
+        <f t="shared" si="7"/>
+        <v>692837.55083333328</v>
+      </c>
+      <c r="E25" s="6">
+        <f t="shared" si="8"/>
+        <v>0.99067248761912463</v>
+      </c>
+      <c r="F25" s="5">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="D25" s="7">
-        <f t="shared" si="3"/>
-        <v>692837.55083333328</v>
-      </c>
-      <c r="E25" s="7">
-        <f t="shared" si="4"/>
-        <v>0.99067248761912463</v>
-      </c>
-      <c r="F25" s="6">
-        <f>INDEX($O$8:$O$19, C25)</f>
         <v>0.98927759250581693</v>
       </c>
-      <c r="G25" s="7">
-        <f t="shared" si="1"/>
+      <c r="G25" s="6">
+        <f t="shared" si="2"/>
         <v>693814.46138027648</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A26" s="25">
+      <c r="A26" s="23">
         <v>43009</v>
       </c>
       <c r="B26" s="3">
         <v>628521.43000000005</v>
       </c>
       <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="D26" s="6">
+        <f t="shared" si="7"/>
+        <v>697660.46875</v>
+      </c>
+      <c r="E26" s="6">
+        <f t="shared" si="8"/>
+        <v>0.9008987296157448</v>
+      </c>
+      <c r="F26" s="5">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="D26" s="7">
-        <f t="shared" si="3"/>
-        <v>697660.46875</v>
-      </c>
-      <c r="E26" s="7">
-        <f t="shared" si="4"/>
-        <v>0.9008987296157448</v>
-      </c>
-      <c r="F26" s="6">
-        <f>INDEX($O$8:$O$19, C26)</f>
         <v>1.0049429687230065</v>
       </c>
-      <c r="G26" s="7">
-        <f t="shared" si="1"/>
+      <c r="G26" s="6">
+        <f t="shared" si="2"/>
         <v>625429.94932206953</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A27" s="24">
+      <c r="A27" s="22">
         <v>43040</v>
       </c>
       <c r="B27" s="2">
         <v>655722.99</v>
       </c>
       <c r="C27" s="2">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="D27" s="6">
+        <f t="shared" si="7"/>
+        <v>717204.38833333342</v>
+      </c>
+      <c r="E27" s="6">
+        <f t="shared" si="8"/>
+        <v>0.91427632159891514</v>
+      </c>
+      <c r="F27" s="5">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="D27" s="7">
-        <f t="shared" si="3"/>
-        <v>717204.38833333342</v>
-      </c>
-      <c r="E27" s="7">
-        <f t="shared" si="4"/>
-        <v>0.91427632159891514</v>
-      </c>
-      <c r="F27" s="6">
-        <f>INDEX($O$8:$O$19, C27)</f>
         <v>1.0813119968257763</v>
       </c>
-      <c r="G27" s="7">
-        <f t="shared" si="1"/>
+      <c r="G27" s="6">
+        <f t="shared" si="2"/>
         <v>606414.23744940816</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A28" s="25">
+      <c r="A28" s="23">
         <v>43070</v>
       </c>
       <c r="B28" s="3">
         <v>1287177.07</v>
       </c>
       <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="D28" s="6">
+        <f t="shared" si="7"/>
+        <v>750506.49791666679</v>
+      </c>
+      <c r="E28" s="6">
+        <f t="shared" si="8"/>
+        <v>1.7150778488568437</v>
+      </c>
+      <c r="F28" s="5">
         <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="D28" s="7">
-        <f t="shared" si="3"/>
-        <v>750506.49791666679</v>
-      </c>
-      <c r="E28" s="7">
-        <f t="shared" si="4"/>
-        <v>1.7150778488568437</v>
-      </c>
-      <c r="F28" s="6">
-        <f>INDEX($O$8:$O$19, C28)</f>
         <v>1.6935272993299522</v>
       </c>
-      <c r="G28" s="7">
-        <f t="shared" si="1"/>
+      <c r="G28" s="6">
+        <f t="shared" si="2"/>
         <v>760056.8768565316</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A29" s="24">
+      <c r="A29" s="22">
         <v>43101</v>
       </c>
       <c r="B29" s="2">
         <v>917075.35</v>
       </c>
       <c r="C29" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="D29" s="6">
+        <f t="shared" si="7"/>
+        <v>783615.1133333334</v>
+      </c>
+      <c r="E29" s="6">
+        <f t="shared" si="8"/>
+        <v>1.1703135051836289</v>
+      </c>
+      <c r="F29" s="5">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D29" s="7">
-        <f t="shared" si="3"/>
-        <v>783615.1133333334</v>
-      </c>
-      <c r="E29" s="7">
-        <f t="shared" si="4"/>
-        <v>1.1703135051836289</v>
-      </c>
-      <c r="F29" s="6">
-        <f>INDEX($O$8:$O$19, C29)</f>
         <v>1.2634175614796064</v>
       </c>
-      <c r="G29" s="7">
-        <f t="shared" si="1"/>
+      <c r="G29" s="6">
+        <f t="shared" si="2"/>
         <v>725868.76893336826</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A30" s="25">
+      <c r="A30" s="23">
         <v>43132</v>
       </c>
       <c r="B30" s="3">
         <v>1344342.7</v>
       </c>
       <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="D30" s="6">
+        <f t="shared" si="7"/>
+        <v>820524.6725000001</v>
+      </c>
+      <c r="E30" s="6">
+        <f t="shared" si="8"/>
+        <v>1.6383939996636723</v>
+      </c>
+      <c r="F30" s="5">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="D30" s="7">
-        <f t="shared" si="3"/>
-        <v>820524.6725000001</v>
-      </c>
-      <c r="E30" s="7">
-        <f t="shared" si="4"/>
-        <v>1.6383939996636723</v>
-      </c>
-      <c r="F30" s="6">
-        <f>INDEX($O$8:$O$19, C30)</f>
         <v>1.4898147904609165</v>
       </c>
-      <c r="G30" s="7">
-        <f t="shared" si="1"/>
+      <c r="G30" s="6">
+        <f t="shared" si="2"/>
         <v>902355.58715596411</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A31" s="24">
+      <c r="A31" s="22">
         <v>43160</v>
       </c>
       <c r="B31" s="2">
         <v>434951.15</v>
       </c>
       <c r="C31" s="2">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="D31" s="6">
+        <f t="shared" si="7"/>
+        <v>859227.03583333339</v>
+      </c>
+      <c r="E31" s="6">
+        <f t="shared" si="8"/>
+        <v>0.50621213237099383</v>
+      </c>
+      <c r="F31" s="5">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="D31" s="7">
-        <f t="shared" si="3"/>
-        <v>859227.03583333339</v>
-      </c>
-      <c r="E31" s="7">
-        <f t="shared" si="4"/>
-        <v>0.50621213237099383</v>
-      </c>
-      <c r="F31" s="6">
-        <f>INDEX($O$8:$O$19, C31)</f>
         <v>0.55770217908347586</v>
       </c>
-      <c r="G31" s="7">
-        <f t="shared" si="1"/>
+      <c r="G31" s="6">
+        <f t="shared" si="2"/>
         <v>779898.60235940968</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A32" s="25">
+      <c r="A32" s="23">
         <v>43191</v>
       </c>
       <c r="B32" s="3">
         <v>70627.539999999994</v>
       </c>
       <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="D32" s="6">
+        <f t="shared" si="7"/>
+        <v>905418.64583333349</v>
+      </c>
+      <c r="E32" s="6">
+        <f t="shared" si="8"/>
+        <v>7.800539598452326E-2</v>
+      </c>
+      <c r="F32" s="5">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="D32" s="7">
-        <f t="shared" si="3"/>
-        <v>905418.64583333349</v>
-      </c>
-      <c r="E32" s="7">
-        <f t="shared" si="4"/>
-        <v>7.800539598452326E-2</v>
-      </c>
-      <c r="F32" s="6">
-        <f>INDEX($O$8:$O$19, C32)</f>
         <v>9.3836861920854581E-2</v>
       </c>
-      <c r="G32" s="7">
-        <f t="shared" si="1"/>
+      <c r="G32" s="6">
+        <f t="shared" si="2"/>
         <v>752663.06389881007</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="24">
+      <c r="A33" s="22">
         <v>43221</v>
       </c>
       <c r="B33" s="2">
         <v>1073265.56</v>
       </c>
       <c r="C33" s="2">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="D33" s="6">
+        <f t="shared" si="7"/>
+        <v>965231.6558333335</v>
+      </c>
+      <c r="E33" s="6">
+        <f t="shared" si="8"/>
+        <v>1.1119253637339477</v>
+      </c>
+      <c r="F33" s="5">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="D33" s="7">
-        <f t="shared" si="3"/>
-        <v>965231.6558333335</v>
-      </c>
-      <c r="E33" s="7">
-        <f t="shared" si="4"/>
-        <v>1.1119253637339477</v>
-      </c>
-      <c r="F33" s="6">
-        <f>INDEX($O$8:$O$19, C33)</f>
         <v>1.0827928889207721</v>
       </c>
-      <c r="G33" s="7">
-        <f t="shared" si="1"/>
+      <c r="G33" s="6">
+        <f t="shared" si="2"/>
         <v>991201.15303835436</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="25">
+      <c r="A34" s="23">
         <v>43252</v>
       </c>
       <c r="B34" s="3">
         <v>973975.33</v>
       </c>
       <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="D34" s="6">
+        <f t="shared" si="7"/>
+        <v>1032620.5145833334</v>
+      </c>
+      <c r="E34" s="6">
+        <f t="shared" si="8"/>
+        <v>0.94320741864498303</v>
+      </c>
+      <c r="F34" s="5">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="D34" s="7">
-        <f t="shared" si="3"/>
-        <v>1032620.5145833334</v>
-      </c>
-      <c r="E34" s="7">
-        <f t="shared" si="4"/>
-        <v>0.94320741864498303</v>
-      </c>
-      <c r="F34" s="6">
-        <f>INDEX($O$8:$O$19, C34)</f>
         <v>0.97911466482353871</v>
       </c>
-      <c r="G34" s="7">
-        <f t="shared" si="1"/>
+      <c r="G34" s="6">
+        <f t="shared" si="2"/>
         <v>994751.03886380361</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="24">
+      <c r="A35" s="22">
         <v>43282</v>
       </c>
       <c r="B35" s="2">
         <v>964149.46</v>
       </c>
       <c r="C35" s="2">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="D35" s="6">
+        <f t="shared" si="7"/>
+        <v>1108406.0641666665</v>
+      </c>
+      <c r="E35" s="6">
+        <f t="shared" si="8"/>
+        <v>0.86985220594663293</v>
+      </c>
+      <c r="F35" s="5">
         <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="D35" s="7">
-        <f t="shared" si="3"/>
-        <v>1108406.0641666665</v>
-      </c>
-      <c r="E35" s="7">
-        <f t="shared" si="4"/>
-        <v>0.86985220594663293</v>
-      </c>
-      <c r="F35" s="6">
-        <f>INDEX($O$8:$O$19, C35)</f>
         <v>0.85333255083444914</v>
       </c>
-      <c r="G35" s="7">
-        <f t="shared" si="1"/>
+      <c r="G35" s="6">
+        <f t="shared" si="2"/>
         <v>1129863.6845121942</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="25">
+      <c r="A36" s="23">
         <v>43313</v>
       </c>
       <c r="B36" s="3">
         <v>1026845.73</v>
       </c>
       <c r="C36" s="3">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="D36" s="6">
+        <f t="shared" si="7"/>
+        <v>1182670.4012499999</v>
+      </c>
+      <c r="E36" s="6">
+        <f t="shared" si="8"/>
+        <v>0.86824336595783225</v>
+      </c>
+      <c r="F36" s="5">
         <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="D36" s="7">
-        <f t="shared" si="3"/>
-        <v>1182670.4012499999</v>
-      </c>
-      <c r="E36" s="7">
-        <f t="shared" si="4"/>
-        <v>0.86824336595783225</v>
-      </c>
-      <c r="F36" s="6">
-        <f>INDEX($O$8:$O$19, C36)</f>
         <v>0.91092864509183669</v>
       </c>
-      <c r="G36" s="7">
-        <f t="shared" si="1"/>
+      <c r="G36" s="6">
+        <f t="shared" si="2"/>
         <v>1127251.5531625168</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="24">
+      <c r="A37" s="22">
         <v>43344</v>
       </c>
       <c r="B37" s="2">
         <v>1181765.1399999999</v>
       </c>
       <c r="C37" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="D37" s="7">
-        <f t="shared" si="3"/>
+      <c r="D37" s="6">
+        <f t="shared" si="7"/>
         <v>1231399.31</v>
       </c>
-      <c r="E37" s="7">
-        <f t="shared" si="4"/>
+      <c r="E37" s="6">
+        <f t="shared" si="8"/>
         <v>0.95969287168107953</v>
       </c>
-      <c r="F37" s="6">
-        <f>INDEX($O$8:$O$19, C37)</f>
+      <c r="F37" s="5">
+        <f t="shared" ref="F37:F66" si="9">INDEX($O$8:$O$19, C37)</f>
         <v>0.98927759250581693</v>
       </c>
-      <c r="G37" s="7">
-        <f t="shared" si="1"/>
+      <c r="G37" s="6">
+        <f t="shared" si="2"/>
         <v>1194573.8475755996</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="25">
+      <c r="A38" s="23">
         <v>43374</v>
       </c>
       <c r="B38" s="3">
         <v>1241730.03</v>
       </c>
       <c r="C38" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="D38" s="7">
-        <f t="shared" si="3"/>
+      <c r="D38" s="6">
+        <f t="shared" si="7"/>
         <v>1251825.9395833334</v>
       </c>
-      <c r="E38" s="7">
-        <f t="shared" si="4"/>
+      <c r="E38" s="6">
+        <f t="shared" si="8"/>
         <v>0.99193505321778697</v>
       </c>
-      <c r="F38" s="6">
-        <f>INDEX($O$8:$O$19, C38)</f>
+      <c r="F38" s="5">
+        <f t="shared" si="9"/>
         <v>1.0049429687230065</v>
       </c>
-      <c r="G38" s="7">
-        <f t="shared" si="1"/>
+      <c r="G38" s="6">
+        <f t="shared" si="2"/>
         <v>1235622.3871866895</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="24">
+      <c r="A39" s="22">
         <v>43405</v>
       </c>
       <c r="B39" s="2">
         <v>1478026.63</v>
       </c>
       <c r="C39" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="D39" s="7">
-        <f t="shared" si="3"/>
+      <c r="D39" s="6">
+        <f t="shared" si="7"/>
         <v>1276844.5262500001</v>
       </c>
-      <c r="E39" s="7">
-        <f t="shared" si="4"/>
+      <c r="E39" s="6">
+        <f t="shared" si="8"/>
         <v>1.1575619424401318</v>
       </c>
-      <c r="F39" s="6">
-        <f>INDEX($O$8:$O$19, C39)</f>
+      <c r="F39" s="5">
+        <f t="shared" si="9"/>
         <v>1.0813119968257763</v>
       </c>
-      <c r="G39" s="7">
-        <f t="shared" si="1"/>
+      <c r="G39" s="6">
+        <f t="shared" si="2"/>
         <v>1366882.6706249365</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="25">
+      <c r="A40" s="23">
         <v>43435</v>
       </c>
       <c r="B40" s="3">
         <v>2082206.04</v>
       </c>
       <c r="C40" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="D40" s="7">
-        <f t="shared" si="3"/>
+      <c r="D40" s="6">
+        <f t="shared" si="7"/>
         <v>1316513.9837500001</v>
       </c>
-      <c r="E40" s="7">
-        <f t="shared" si="4"/>
+      <c r="E40" s="6">
+        <f t="shared" si="8"/>
         <v>1.581605714562164</v>
       </c>
-      <c r="F40" s="6">
-        <f>INDEX($O$8:$O$19, C40)</f>
+      <c r="F40" s="5">
+        <f t="shared" si="9"/>
         <v>1.6935272993299522</v>
       </c>
-      <c r="G40" s="7">
-        <f t="shared" si="1"/>
+      <c r="G40" s="6">
+        <f t="shared" si="2"/>
         <v>1229508.3999081855</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="24">
+      <c r="A41" s="22">
         <v>43466</v>
       </c>
       <c r="B41" s="2">
         <v>1940899.57</v>
       </c>
       <c r="C41" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="D41" s="7">
-        <f t="shared" si="3"/>
+      <c r="D41" s="6">
+        <f t="shared" si="7"/>
         <v>1352991.1183333336</v>
       </c>
-      <c r="E41" s="7">
-        <f t="shared" si="4"/>
+      <c r="E41" s="6">
+        <f t="shared" si="8"/>
         <v>1.4345249896325074</v>
       </c>
-      <c r="F41" s="6">
-        <f>INDEX($O$8:$O$19, C41)</f>
+      <c r="F41" s="5">
+        <f t="shared" si="9"/>
         <v>1.2634175614796064</v>
       </c>
-      <c r="G41" s="7">
-        <f t="shared" si="1"/>
+      <c r="G41" s="6">
+        <f t="shared" si="2"/>
         <v>1536229.6909400127</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="25">
+      <c r="A42" s="23">
         <v>43497</v>
       </c>
       <c r="B42" s="3">
         <v>2102862.5699999998</v>
       </c>
       <c r="C42" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="D42" s="7">
-        <f t="shared" si="3"/>
+      <c r="D42" s="6">
+        <f t="shared" si="7"/>
         <v>1391262.1266666669</v>
       </c>
-      <c r="E42" s="7">
-        <f t="shared" si="4"/>
+      <c r="E42" s="6">
+        <f t="shared" si="8"/>
         <v>1.5114783402019722</v>
       </c>
-      <c r="F42" s="6">
-        <f>INDEX($O$8:$O$19, C42)</f>
+      <c r="F42" s="5">
+        <f t="shared" si="9"/>
         <v>1.4898147904609165</v>
       </c>
-      <c r="G42" s="7">
-        <f t="shared" si="1"/>
+      <c r="G42" s="6">
+        <f t="shared" si="2"/>
         <v>1411492.6120107986</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="24">
+      <c r="A43" s="22">
         <v>43525</v>
       </c>
       <c r="B43" s="2">
         <v>845925.09</v>
       </c>
       <c r="C43" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="D43" s="7">
-        <f t="shared" si="3"/>
+      <c r="D43" s="6">
+        <f t="shared" si="7"/>
         <v>1426263.9862500001</v>
       </c>
-      <c r="E43" s="7">
-        <f t="shared" si="4"/>
+      <c r="E43" s="6">
+        <f t="shared" si="8"/>
         <v>0.59310555279751942</v>
       </c>
-      <c r="F43" s="6">
-        <f>INDEX($O$8:$O$19, C43)</f>
+      <c r="F43" s="5">
+        <f t="shared" si="9"/>
         <v>0.55770217908347586</v>
       </c>
-      <c r="G43" s="7">
-        <f t="shared" si="1"/>
+      <c r="G43" s="6">
+        <f t="shared" si="2"/>
         <v>1516804.3477796479</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="25">
+      <c r="A44" s="23">
         <v>43556</v>
       </c>
       <c r="B44" s="3">
         <v>149892.71</v>
       </c>
       <c r="C44" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="D44" s="7">
-        <f t="shared" si="3"/>
+      <c r="D44" s="6">
+        <f t="shared" si="7"/>
         <v>1455411.6687500002</v>
       </c>
-      <c r="E44" s="7">
-        <f t="shared" si="4"/>
+      <c r="E44" s="6">
+        <f t="shared" si="8"/>
         <v>0.10298990534323348</v>
       </c>
-      <c r="F44" s="6">
-        <f>INDEX($O$8:$O$19, C44)</f>
+      <c r="F44" s="5">
+        <f t="shared" si="9"/>
         <v>9.3836861920854581E-2</v>
       </c>
-      <c r="G44" s="7">
-        <f t="shared" si="1"/>
+      <c r="G44" s="6">
+        <f t="shared" si="2"/>
         <v>1597375.5614976229</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="24">
+      <c r="A45" s="22">
         <v>43586</v>
       </c>
       <c r="B45" s="2">
         <v>1594446.47</v>
       </c>
       <c r="C45" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="D45" s="7">
-        <f t="shared" si="3"/>
+      <c r="D45" s="6">
+        <f t="shared" si="7"/>
         <v>1479206.3370833334</v>
       </c>
-      <c r="E45" s="7">
-        <f t="shared" si="4"/>
+      <c r="E45" s="6">
+        <f t="shared" si="8"/>
         <v>1.0779067328388374</v>
       </c>
-      <c r="F45" s="6">
-        <f>INDEX($O$8:$O$19, C45)</f>
+      <c r="F45" s="5">
+        <f t="shared" si="9"/>
         <v>1.0827928889207721</v>
       </c>
-      <c r="G45" s="7">
-        <f t="shared" si="1"/>
+      <c r="G45" s="6">
+        <f t="shared" si="2"/>
         <v>1472531.3458506335</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="25">
+      <c r="A46" s="23">
         <v>43617</v>
       </c>
       <c r="B46" s="3">
         <v>1404861.4</v>
       </c>
       <c r="C46" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="D46" s="7">
-        <f t="shared" si="3"/>
+      <c r="D46" s="6">
+        <f t="shared" si="7"/>
         <v>1505569.7979166666</v>
       </c>
-      <c r="E46" s="7">
-        <f t="shared" si="4"/>
+      <c r="E46" s="6">
+        <f t="shared" si="8"/>
         <v>0.93310944596788403</v>
       </c>
-      <c r="F46" s="6">
-        <f>INDEX($O$8:$O$19, C46)</f>
+      <c r="F46" s="5">
+        <f t="shared" si="9"/>
         <v>0.97911466482353871</v>
       </c>
-      <c r="G46" s="7">
-        <f t="shared" si="1"/>
+      <c r="G46" s="6">
+        <f t="shared" si="2"/>
         <v>1434828.2693255253</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="24">
+      <c r="A47" s="22">
         <v>43647</v>
       </c>
       <c r="B47" s="2">
         <v>1408714.62</v>
       </c>
       <c r="C47" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="D47" s="7">
-        <f t="shared" si="3"/>
+      <c r="D47" s="6">
+        <f t="shared" si="7"/>
         <v>1527367.3545833332</v>
       </c>
-      <c r="E47" s="7">
-        <f t="shared" si="4"/>
+      <c r="E47" s="6">
+        <f t="shared" si="8"/>
         <v>0.92231552270167405</v>
       </c>
-      <c r="F47" s="6">
-        <f>INDEX($O$8:$O$19, C47)</f>
+      <c r="F47" s="5">
+        <f t="shared" si="9"/>
         <v>0.85333255083444914</v>
       </c>
-      <c r="G47" s="7">
-        <f t="shared" si="1"/>
+      <c r="G47" s="6">
+        <f t="shared" si="2"/>
         <v>1650838.95911677</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="25">
+      <c r="A48" s="23">
         <v>43678</v>
       </c>
       <c r="B48" s="3">
         <v>1500784.77</v>
       </c>
       <c r="C48" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D48" s="7">
-        <f t="shared" si="3"/>
+      <c r="D48" s="6">
+        <f t="shared" si="7"/>
         <v>1537891.0441666669</v>
       </c>
-      <c r="E48" s="7">
-        <f t="shared" si="4"/>
+      <c r="E48" s="6">
+        <f t="shared" si="8"/>
         <v>0.97587197460612463</v>
       </c>
-      <c r="F48" s="6">
-        <f>INDEX($O$8:$O$19, C48)</f>
+      <c r="F48" s="5">
+        <f t="shared" si="9"/>
         <v>0.91092864509183669</v>
       </c>
-      <c r="G48" s="7">
-        <f t="shared" si="1"/>
+      <c r="G48" s="6">
+        <f t="shared" si="2"/>
         <v>1647532.743740533</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="24">
+      <c r="A49" s="22">
         <v>43709</v>
       </c>
       <c r="B49" s="2">
         <v>1547870.73</v>
       </c>
       <c r="C49" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="D49" s="7">
-        <f t="shared" si="3"/>
+      <c r="D49" s="6">
+        <f t="shared" si="7"/>
         <v>1535956.9845833336</v>
       </c>
-      <c r="E49" s="7">
-        <f t="shared" si="4"/>
+      <c r="E49" s="6">
+        <f t="shared" si="8"/>
         <v>1.0077565618934949</v>
       </c>
-      <c r="F49" s="6">
-        <f>INDEX($O$8:$O$19, C49)</f>
+      <c r="F49" s="5">
+        <f t="shared" si="9"/>
         <v>0.98927759250581693</v>
       </c>
-      <c r="G49" s="7">
-        <f t="shared" si="1"/>
+      <c r="G49" s="6">
+        <f t="shared" si="2"/>
         <v>1564647.5182757145</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="25">
+      <c r="A50" s="23">
         <v>43739</v>
       </c>
       <c r="B50" s="3">
         <v>1575168.82</v>
       </c>
       <c r="C50" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="D50" s="7">
-        <f t="shared" si="3"/>
+      <c r="D50" s="6">
+        <f t="shared" si="7"/>
         <v>1531657.6079166667</v>
       </c>
-      <c r="E50" s="7">
-        <f t="shared" si="4"/>
+      <c r="E50" s="6">
+        <f t="shared" si="8"/>
         <v>1.0284079234539347</v>
       </c>
-      <c r="F50" s="6">
-        <f>INDEX($O$8:$O$19, C50)</f>
+      <c r="F50" s="5">
+        <f t="shared" si="9"/>
         <v>1.0049429687230065</v>
       </c>
-      <c r="G50" s="7">
-        <f t="shared" si="1"/>
+      <c r="G50" s="6">
+        <f t="shared" si="2"/>
         <v>1567421.106494816</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" s="24">
+      <c r="A51" s="22">
         <v>43770</v>
       </c>
       <c r="B51" s="2">
         <v>1715659.88</v>
       </c>
       <c r="C51" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="D51" s="7">
-        <f t="shared" si="3"/>
+      <c r="D51" s="6">
+        <f t="shared" si="7"/>
         <v>1504629.6724999999</v>
       </c>
-      <c r="E51" s="7">
-        <f t="shared" si="4"/>
+      <c r="E51" s="6">
+        <f t="shared" si="8"/>
         <v>1.1402539185269192</v>
       </c>
-      <c r="F51" s="6">
-        <f>INDEX($O$8:$O$19, C51)</f>
+      <c r="F51" s="5">
+        <f t="shared" si="9"/>
         <v>1.0813119968257763</v>
       </c>
-      <c r="G51" s="7">
-        <f t="shared" si="1"/>
+      <c r="G51" s="6">
+        <f t="shared" si="2"/>
         <v>1586646.4859692398</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="25">
+      <c r="A52" s="23">
         <v>43800</v>
       </c>
       <c r="B52" s="3">
         <v>2477295.85</v>
       </c>
       <c r="C52" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="D52" s="7">
-        <f t="shared" si="3"/>
+      <c r="D52" s="6">
+        <f t="shared" si="7"/>
         <v>1448071.4220833331</v>
       </c>
-      <c r="E52" s="7">
-        <f t="shared" si="4"/>
+      <c r="E52" s="6">
+        <f t="shared" si="8"/>
         <v>1.7107552930199581</v>
       </c>
-      <c r="F52" s="6">
-        <f>INDEX($O$8:$O$19, C52)</f>
+      <c r="F52" s="5">
+        <f t="shared" si="9"/>
         <v>1.6935272993299522</v>
       </c>
-      <c r="G52" s="7">
-        <f t="shared" si="1"/>
+      <c r="G52" s="6">
+        <f t="shared" si="2"/>
         <v>1462802.4307492108</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" s="24">
+      <c r="A53" s="22">
         <v>43831</v>
       </c>
       <c r="B53" s="2">
         <v>2068951.12</v>
       </c>
       <c r="C53" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="D53" s="7">
-        <f t="shared" si="3"/>
+      <c r="D53" s="6">
+        <f t="shared" si="7"/>
         <v>1384034.4383333335</v>
       </c>
-      <c r="E53" s="7">
-        <f t="shared" si="4"/>
+      <c r="E53" s="6">
+        <f t="shared" si="8"/>
         <v>1.4948696814881639</v>
       </c>
-      <c r="F53" s="6">
-        <f>INDEX($O$8:$O$19, C53)</f>
+      <c r="F53" s="5">
+        <f t="shared" si="9"/>
         <v>1.2634175614796064</v>
       </c>
-      <c r="G53" s="7">
-        <f t="shared" si="1"/>
+      <c r="G53" s="6">
+        <f t="shared" si="2"/>
         <v>1637582.9995405651</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54" s="25">
+      <c r="A54" s="23">
         <v>43862</v>
       </c>
       <c r="B54" s="3">
         <v>2227379.5699999998</v>
       </c>
       <c r="C54" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="D54" s="7">
-        <f t="shared" si="3"/>
+      <c r="D54" s="6">
+        <f t="shared" si="7"/>
         <v>1301532.4745833334</v>
       </c>
-      <c r="E54" s="7">
-        <f t="shared" si="4"/>
+      <c r="E54" s="6">
+        <f t="shared" si="8"/>
         <v>1.7113515133097719</v>
       </c>
-      <c r="F54" s="6">
-        <f>INDEX($O$8:$O$19, C54)</f>
+      <c r="F54" s="5">
+        <f t="shared" si="9"/>
         <v>1.4898147904609165</v>
       </c>
-      <c r="G54" s="7">
-        <f t="shared" si="1"/>
+      <c r="G54" s="6">
+        <f t="shared" si="2"/>
         <v>1495071.4573795423</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55" s="24">
+      <c r="A55" s="22">
         <v>43891</v>
       </c>
       <c r="B55" s="2">
         <v>674990.66</v>
       </c>
       <c r="C55" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="D55" s="7">
-        <f t="shared" si="3"/>
+      <c r="D55" s="6">
+        <f t="shared" si="7"/>
         <v>1207716.7704166668</v>
       </c>
-      <c r="E55" s="7">
-        <f t="shared" si="4"/>
+      <c r="E55" s="6">
+        <f t="shared" si="8"/>
         <v>0.55889814278816863</v>
       </c>
-      <c r="F55" s="6">
-        <f>INDEX($O$8:$O$19, C55)</f>
+      <c r="F55" s="5">
+        <f t="shared" si="9"/>
         <v>0.55770217908347586</v>
       </c>
-      <c r="G55" s="7">
-        <f t="shared" si="1"/>
+      <c r="G55" s="6">
+        <f t="shared" si="2"/>
         <v>1210306.6570571328</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56" s="25">
+      <c r="A56" s="23">
         <v>43922</v>
       </c>
       <c r="B56" s="3">
         <v>217642.1</v>
       </c>
       <c r="C56" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="D56" s="7">
-        <f t="shared" si="3"/>
+      <c r="D56" s="6">
+        <f t="shared" si="7"/>
         <v>1103676.7520833332</v>
       </c>
-      <c r="E56" s="7">
-        <f t="shared" si="4"/>
+      <c r="E56" s="6">
+        <f t="shared" si="8"/>
         <v>0.19719732212277941</v>
       </c>
-      <c r="F56" s="6">
-        <f>INDEX($O$8:$O$19, C56)</f>
+      <c r="F56" s="5">
+        <f t="shared" si="9"/>
         <v>9.3836861920854581E-2</v>
       </c>
-      <c r="G56" s="7">
-        <f t="shared" si="1"/>
+      <c r="G56" s="6">
+        <f t="shared" si="2"/>
         <v>2319366.777030196</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" s="24">
+      <c r="A57" s="22">
         <v>43952</v>
       </c>
       <c r="B57" s="2">
         <v>878026.63</v>
       </c>
       <c r="C57" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="D57" s="7">
-        <f t="shared" si="3"/>
+      <c r="D57" s="6">
+        <f t="shared" si="7"/>
         <v>987490.08166666678</v>
       </c>
-      <c r="E57" s="7">
-        <f t="shared" si="4"/>
+      <c r="E57" s="6">
+        <f t="shared" si="8"/>
         <v>0.88914982165500189</v>
       </c>
-      <c r="F57" s="6">
-        <f>INDEX($O$8:$O$19, C57)</f>
+      <c r="F57" s="5">
+        <f t="shared" si="9"/>
         <v>1.0827928889207721</v>
       </c>
-      <c r="G57" s="7">
-        <f t="shared" si="1"/>
+      <c r="G57" s="6">
+        <f t="shared" si="2"/>
         <v>810890.65045036993</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" s="25">
+      <c r="A58" s="23">
         <v>43983</v>
       </c>
       <c r="B58" s="3">
         <v>763883.23</v>
       </c>
       <c r="C58" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="D58" s="7">
-        <f t="shared" si="3"/>
+      <c r="D58" s="6">
+        <f t="shared" si="7"/>
         <v>850626.40374999994</v>
       </c>
-      <c r="E58" s="7">
-        <f t="shared" si="4"/>
+      <c r="E58" s="6">
+        <f t="shared" si="8"/>
         <v>0.89802435785252921</v>
       </c>
-      <c r="F58" s="6">
-        <f>INDEX($O$8:$O$19, C58)</f>
+      <c r="F58" s="5">
+        <f t="shared" si="9"/>
         <v>0.97911466482353871</v>
       </c>
-      <c r="G58" s="7">
-        <f t="shared" si="1"/>
+      <c r="G58" s="6">
+        <f t="shared" si="2"/>
         <v>780177.49855444266</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" s="24">
+      <c r="A59" s="22">
         <v>44013</v>
       </c>
       <c r="B59" s="2">
         <v>512805.18</v>
       </c>
       <c r="C59" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="D59" s="7">
-        <f t="shared" si="3"/>
+      <c r="D59" s="6">
+        <f t="shared" si="7"/>
         <v>709722.28083333315</v>
       </c>
-      <c r="E59" s="7">
-        <f t="shared" si="4"/>
+      <c r="E59" s="6">
+        <f t="shared" si="8"/>
         <v>0.72254344248271396</v>
       </c>
-      <c r="F59" s="6">
-        <f>INDEX($O$8:$O$19, C59)</f>
+      <c r="F59" s="5">
+        <f t="shared" si="9"/>
         <v>0.85333255083444914</v>
       </c>
-      <c r="G59" s="7">
-        <f t="shared" si="1"/>
+      <c r="G59" s="6">
+        <f t="shared" si="2"/>
         <v>600944.12137277867</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" s="25">
+      <c r="A60" s="23">
         <v>44044</v>
       </c>
       <c r="B60" s="3">
         <v>416647.08</v>
       </c>
       <c r="C60" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D60" s="7">
-        <f t="shared" si="3"/>
+      <c r="D60" s="6">
+        <f t="shared" si="7"/>
         <v>574012.18874999997</v>
       </c>
-      <c r="E60" s="7">
-        <f t="shared" si="4"/>
+      <c r="E60" s="6">
+        <f t="shared" si="8"/>
         <v>0.72585057977133427</v>
       </c>
-      <c r="F60" s="6">
-        <f>INDEX($O$8:$O$19, C60)</f>
+      <c r="F60" s="5">
+        <f t="shared" si="9"/>
         <v>0.91092864509183669</v>
       </c>
-      <c r="G60" s="7">
-        <f t="shared" si="1"/>
+      <c r="G60" s="6">
+        <f t="shared" si="2"/>
         <v>457387.17543347768</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" s="24">
+      <c r="A61" s="22">
         <v>44075</v>
       </c>
       <c r="B61" s="2">
         <v>380431.52</v>
       </c>
       <c r="C61" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="E61" s="7"/>
-      <c r="F61" s="6">
-        <f>INDEX($O$8:$O$19, C61)</f>
+      <c r="E61" s="6"/>
+      <c r="F61" s="5">
+        <f t="shared" si="9"/>
         <v>0.98927759250581693</v>
       </c>
-      <c r="G61" s="7">
-        <f t="shared" si="1"/>
+      <c r="G61" s="6">
+        <f t="shared" si="2"/>
         <v>384554.87406358402</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" s="25">
+      <c r="A62" s="23">
         <v>44105</v>
       </c>
       <c r="B62" s="3">
         <v>245647.59</v>
       </c>
       <c r="C62" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="E62" s="7"/>
-      <c r="F62" s="6">
-        <f>INDEX($O$8:$O$19, C62)</f>
+      <c r="E62" s="6"/>
+      <c r="F62" s="5">
+        <f t="shared" si="9"/>
         <v>1.0049429687230065</v>
       </c>
-      <c r="G62" s="7">
-        <f t="shared" si="1"/>
+      <c r="G62" s="6">
+        <f t="shared" si="2"/>
         <v>244439.33401728005</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" s="24">
+      <c r="A63" s="22">
         <v>44136</v>
       </c>
       <c r="B63" s="2">
         <v>256701.02</v>
       </c>
       <c r="C63" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="E63" s="7"/>
-      <c r="F63" s="6">
-        <f>INDEX($O$8:$O$19, C63)</f>
+      <c r="E63" s="6"/>
+      <c r="F63" s="5">
+        <f t="shared" si="9"/>
         <v>1.0813119968257763</v>
       </c>
-      <c r="G63" s="7">
-        <f t="shared" si="1"/>
+      <c r="G63" s="6">
+        <f t="shared" si="2"/>
         <v>237397.73604061874</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" s="25">
+      <c r="A64" s="23">
         <v>44166</v>
       </c>
       <c r="B64" s="3">
         <v>651526.43999999994</v>
       </c>
       <c r="C64" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="E64" s="7"/>
-      <c r="F64" s="6">
-        <f>INDEX($O$8:$O$19, C64)</f>
+      <c r="E64" s="6"/>
+      <c r="F64" s="5">
+        <f t="shared" si="9"/>
         <v>1.6935272993299522</v>
       </c>
-      <c r="G64" s="7">
-        <f t="shared" si="1"/>
+      <c r="G64" s="6">
+        <f t="shared" si="2"/>
         <v>384715.64069724642</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" s="24">
+      <c r="A65" s="22">
         <v>44197</v>
       </c>
       <c r="B65" s="2">
         <v>513021.58</v>
       </c>
       <c r="C65" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E65" s="7"/>
-      <c r="F65" s="6">
-        <f>INDEX($O$8:$O$19, C65)</f>
+      <c r="E65" s="6"/>
+      <c r="F65" s="5">
+        <f t="shared" si="9"/>
         <v>1.2634175614796064</v>
       </c>
-      <c r="G65" s="7">
-        <f t="shared" si="1"/>
+      <c r="G65" s="6">
+        <f t="shared" si="2"/>
         <v>406058.61089914967</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="26">
+      <c r="A66" s="24">
         <v>44228</v>
       </c>
       <c r="B66" s="4">
         <v>526266.9</v>
       </c>
       <c r="C66" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="E66" s="7"/>
-      <c r="F66" s="6">
-        <f>INDEX($O$8:$O$19, C66)</f>
+      <c r="E66" s="6"/>
+      <c r="F66" s="5">
+        <f t="shared" si="9"/>
         <v>1.4898147904609165</v>
       </c>
-      <c r="G66" s="7">
-        <f t="shared" si="1"/>
+      <c r="G66" s="6">
+        <f t="shared" si="2"/>
         <v>353243.17047301191</v>
       </c>
     </row>
@@ -8115,35 +8106,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="11" t="s">
-        <v>75</v>
+      <c r="A1" s="9" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="42" t="s">
+      <c r="C4" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="42" t="s">
+      <c r="D4" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="42" t="s">
+      <c r="E4" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="42" t="s">
+      <c r="G4" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="42" t="s">
+      <c r="H4" s="38" t="s">
         <v>12</v>
       </c>
     </row>
@@ -8157,7 +8148,7 @@
       <c r="G5" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="8">
         <f>_xlfn.FORECAST.ETS.STAT($B$5:$B$66,$A$5:$A$66,1,1,1)</f>
         <v>2E-3</v>
       </c>
@@ -8172,7 +8163,7 @@
       <c r="G6" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="8">
         <f>_xlfn.FORECAST.ETS.STAT($B$5:$B$66,$A$5:$A$66,2,1,1)</f>
         <v>1E-3</v>
       </c>
@@ -8187,7 +8178,7 @@
       <c r="G7" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="8">
         <f>_xlfn.FORECAST.ETS.STAT($B$5:$B$66,$A$5:$A$66,3,1,1)</f>
         <v>2.2204460492503131E-16</v>
       </c>
@@ -8202,7 +8193,7 @@
       <c r="G8" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="8">
         <f>_xlfn.FORECAST.ETS.STAT($B$5:$B$66,$A$5:$A$66,4,1,1)</f>
         <v>2.2647329906694078</v>
       </c>
@@ -8217,7 +8208,7 @@
       <c r="G9" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="8">
         <f>_xlfn.FORECAST.ETS.STAT($B$5:$B$66,$A$5:$A$66,5,1,1)</f>
         <v>0.81410631794336752</v>
       </c>
@@ -8232,7 +8223,7 @@
       <c r="G10" t="s">
         <v>18</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="8">
         <f>_xlfn.FORECAST.ETS.STAT($B$5:$B$66,$A$5:$A$66,6,1,1)</f>
         <v>686423.7094784209</v>
       </c>
@@ -8247,7 +8238,7 @@
       <c r="G11" t="s">
         <v>19</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="8">
         <f>_xlfn.FORECAST.ETS.STAT($B$5:$B$66,$A$5:$A$66,7,1,1)</f>
         <v>731288.83573381184</v>
       </c>
@@ -8694,10 +8685,10 @@
       <c r="C66">
         <v>526266.9</v>
       </c>
-      <c r="D66" s="7">
+      <c r="D66" s="6">
         <v>526266.9</v>
       </c>
-      <c r="E66" s="7">
+      <c r="E66" s="6">
         <v>526266.9</v>
       </c>
     </row>
@@ -8706,15 +8697,15 @@
         <v>63</v>
       </c>
       <c r="C67">
-        <f>_xlfn.FORECAST.ETS(A67,$B$5:$B$66,$A$5:$A$66,1,1)</f>
+        <f t="shared" ref="C67:C78" si="0">_xlfn.FORECAST.ETS(A67,$B$5:$B$66,$A$5:$A$66,1,1)</f>
         <v>1218834.3721551797</v>
       </c>
-      <c r="D67" s="7">
-        <f>C67-_xlfn.FORECAST.ETS.CONFINT(A67,$B$5:$B$66,$A$5:$A$66,0.95,1,1)</f>
+      <c r="D67" s="6">
+        <f t="shared" ref="D67:D78" si="1">C67-_xlfn.FORECAST.ETS.CONFINT(A67,$B$5:$B$66,$A$5:$A$66,0.95,1,1)</f>
         <v>85934.483010561438</v>
       </c>
-      <c r="E67" s="7">
-        <f>C67+_xlfn.FORECAST.ETS.CONFINT(A67,$B$5:$B$66,$A$5:$A$66,0.95,1,1)</f>
+      <c r="E67" s="6">
+        <f t="shared" ref="E67:E78" si="2">C67+_xlfn.FORECAST.ETS.CONFINT(A67,$B$5:$B$66,$A$5:$A$66,0.95,1,1)</f>
         <v>2351734.2612997983</v>
       </c>
     </row>
@@ -8723,15 +8714,15 @@
         <v>64</v>
       </c>
       <c r="C68">
-        <f>_xlfn.FORECAST.ETS(A68,$B$5:$B$66,$A$5:$A$66,1,1)</f>
+        <f t="shared" si="0"/>
         <v>1228354.6653142003</v>
       </c>
-      <c r="D68" s="7">
-        <f>C68-_xlfn.FORECAST.ETS.CONFINT(A68,$B$5:$B$66,$A$5:$A$66,0.95,1,1)</f>
+      <c r="D68" s="6">
+        <f t="shared" si="1"/>
         <v>95449.678131551482</v>
       </c>
-      <c r="E68" s="7">
-        <f>C68+_xlfn.FORECAST.ETS.CONFINT(A68,$B$5:$B$66,$A$5:$A$66,0.95,1,1)</f>
+      <c r="E68" s="6">
+        <f t="shared" si="2"/>
         <v>2361259.6524968492</v>
       </c>
     </row>
@@ -8740,15 +8731,15 @@
         <v>65</v>
       </c>
       <c r="C69">
-        <f>_xlfn.FORECAST.ETS(A69,$B$5:$B$66,$A$5:$A$66,1,1)</f>
+        <f t="shared" si="0"/>
         <v>1237874.9584732198</v>
       </c>
-      <c r="D69" s="7">
-        <f>C69-_xlfn.FORECAST.ETS.CONFINT(A69,$B$5:$B$66,$A$5:$A$66,0.95,1,1)</f>
+      <c r="D69" s="6">
+        <f t="shared" si="1"/>
         <v>104960.90816849377</v>
       </c>
-      <c r="E69" s="7">
-        <f>C69+_xlfn.FORECAST.ETS.CONFINT(A69,$B$5:$B$66,$A$5:$A$66,0.95,1,1)</f>
+      <c r="E69" s="6">
+        <f t="shared" si="2"/>
         <v>2370789.0087779458</v>
       </c>
     </row>
@@ -8757,15 +8748,15 @@
         <v>66</v>
       </c>
       <c r="C70">
-        <f>_xlfn.FORECAST.ETS(A70,$B$5:$B$66,$A$5:$A$66,1,1)</f>
+        <f t="shared" si="0"/>
         <v>1247395.2516322404</v>
       </c>
-      <c r="D70" s="7">
-        <f>C70-_xlfn.FORECAST.ETS.CONFINT(A70,$B$5:$B$66,$A$5:$A$66,0.95,1,1)</f>
+      <c r="D70" s="6">
+        <f t="shared" si="1"/>
         <v>114467.04034441593</v>
       </c>
-      <c r="E70" s="7">
-        <f>C70+_xlfn.FORECAST.ETS.CONFINT(A70,$B$5:$B$66,$A$5:$A$66,0.95,1,1)</f>
+      <c r="E70" s="6">
+        <f t="shared" si="2"/>
         <v>2380323.462920065</v>
       </c>
     </row>
@@ -8774,15 +8765,15 @@
         <v>67</v>
       </c>
       <c r="C71">
-        <f>_xlfn.FORECAST.ETS(A71,$B$5:$B$66,$A$5:$A$66,1,1)</f>
+        <f t="shared" si="0"/>
         <v>1256915.54479126</v>
       </c>
-      <c r="D71" s="7">
-        <f>C71-_xlfn.FORECAST.ETS.CONFINT(A71,$B$5:$B$66,$A$5:$A$66,0.95,1,1)</f>
+      <c r="D71" s="6">
+        <f t="shared" si="1"/>
         <v>123966.94199872948</v>
       </c>
-      <c r="E71" s="7">
-        <f>C71+_xlfn.FORECAST.ETS.CONFINT(A71,$B$5:$B$66,$A$5:$A$66,0.95,1,1)</f>
+      <c r="E71" s="6">
+        <f t="shared" si="2"/>
         <v>2389864.1475837906</v>
       </c>
     </row>
@@ -8791,15 +8782,15 @@
         <v>68</v>
       </c>
       <c r="C72">
-        <f>_xlfn.FORECAST.ETS(A72,$B$5:$B$66,$A$5:$A$66,1,1)</f>
+        <f t="shared" si="0"/>
         <v>1266435.8379502806</v>
       </c>
-      <c r="D72" s="7">
-        <f>C72-_xlfn.FORECAST.ETS.CONFINT(A72,$B$5:$B$66,$A$5:$A$66,0.95,1,1)</f>
+      <c r="D72" s="6">
+        <f t="shared" si="1"/>
         <v>133459.48064385843</v>
       </c>
-      <c r="E72" s="7">
-        <f>C72+_xlfn.FORECAST.ETS.CONFINT(A72,$B$5:$B$66,$A$5:$A$66,0.95,1,1)</f>
+      <c r="E72" s="6">
+        <f t="shared" si="2"/>
         <v>2399412.1952567026</v>
       </c>
     </row>
@@ -8808,15 +8799,15 @@
         <v>69</v>
       </c>
       <c r="C73">
-        <f>_xlfn.FORECAST.ETS(A73,$B$5:$B$66,$A$5:$A$66,1,1)</f>
+        <f t="shared" si="0"/>
         <v>1275956.1311093003</v>
       </c>
-      <c r="D73" s="7">
-        <f>C73-_xlfn.FORECAST.ETS.CONFINT(A73,$B$5:$B$66,$A$5:$A$66,0.95,1,1)</f>
+      <c r="D73" s="6">
+        <f t="shared" si="1"/>
         <v>142943.52403315017</v>
       </c>
-      <c r="E73" s="7">
-        <f>C73+_xlfn.FORECAST.ETS.CONFINT(A73,$B$5:$B$66,$A$5:$A$66,0.95,1,1)</f>
+      <c r="E73" s="6">
+        <f t="shared" si="2"/>
         <v>2408968.7381854504</v>
       </c>
     </row>
@@ -8825,15 +8816,15 @@
         <v>70</v>
       </c>
       <c r="C74">
-        <f>_xlfn.FORECAST.ETS(A74,$B$5:$B$66,$A$5:$A$66,1,1)</f>
+        <f t="shared" si="0"/>
         <v>1285476.4242683207</v>
       </c>
-      <c r="D74" s="7">
-        <f>C74-_xlfn.FORECAST.ETS.CONFINT(A74,$B$5:$B$66,$A$5:$A$66,0.95,1,1)</f>
+      <c r="D74" s="6">
+        <f t="shared" si="1"/>
         <v>152417.94024008699</v>
       </c>
-      <c r="E74" s="7">
-        <f>C74+_xlfn.FORECAST.ETS.CONFINT(A74,$B$5:$B$66,$A$5:$A$66,0.95,1,1)</f>
+      <c r="E74" s="6">
+        <f t="shared" si="2"/>
         <v>2418534.9082965543</v>
       </c>
     </row>
@@ -8842,15 +8833,15 @@
         <v>71</v>
       </c>
       <c r="C75">
-        <f>_xlfn.FORECAST.ETS(A75,$B$5:$B$66,$A$5:$A$66,1,1)</f>
+        <f t="shared" si="0"/>
         <v>1294996.7174273403</v>
       </c>
-      <c r="D75" s="7">
-        <f>C75-_xlfn.FORECAST.ETS.CONFINT(A75,$B$5:$B$66,$A$5:$A$66,0.95,1,1)</f>
+      <c r="D75" s="6">
+        <f t="shared" si="1"/>
         <v>161881.59774874314</v>
       </c>
-      <c r="E75" s="7">
-        <f>C75+_xlfn.FORECAST.ETS.CONFINT(A75,$B$5:$B$66,$A$5:$A$66,0.95,1,1)</f>
+      <c r="E75" s="6">
+        <f t="shared" si="2"/>
         <v>2428111.8371059373</v>
       </c>
     </row>
@@ -8859,15 +8850,15 @@
         <v>72</v>
       </c>
       <c r="C76">
-        <f>_xlfn.FORECAST.ETS(A76,$B$5:$B$66,$A$5:$A$66,1,1)</f>
+        <f t="shared" si="0"/>
         <v>1304517.0105863609</v>
       </c>
-      <c r="D76" s="7">
-        <f>C76-_xlfn.FORECAST.ETS.CONFINT(A76,$B$5:$B$66,$A$5:$A$66,0.95,1,1)</f>
+      <c r="D76" s="6">
+        <f t="shared" si="1"/>
         <v>171333.36555548618</v>
       </c>
-      <c r="E76" s="7">
-        <f>C76+_xlfn.FORECAST.ETS.CONFINT(A76,$B$5:$B$66,$A$5:$A$66,0.95,1,1)</f>
+      <c r="E76" s="6">
+        <f t="shared" si="2"/>
         <v>2437700.6556172357</v>
       </c>
     </row>
@@ -8876,15 +8867,15 @@
         <v>73</v>
       </c>
       <c r="C77">
-        <f>_xlfn.FORECAST.ETS(A77,$B$5:$B$66,$A$5:$A$66,1,1)</f>
+        <f t="shared" si="0"/>
         <v>1314037.3037453806</v>
       </c>
-      <c r="D77" s="7">
-        <f>C77-_xlfn.FORECAST.ETS.CONFINT(A77,$B$5:$B$66,$A$5:$A$66,0.95,1,1)</f>
+      <c r="D77" s="6">
+        <f t="shared" si="1"/>
         <v>180772.11328185559</v>
       </c>
-      <c r="E77" s="7">
-        <f>C77+_xlfn.FORECAST.ETS.CONFINT(A77,$B$5:$B$66,$A$5:$A$66,0.95,1,1)</f>
+      <c r="E77" s="6">
+        <f t="shared" si="2"/>
         <v>2447302.4942089058</v>
       </c>
     </row>
@@ -8893,297 +8884,297 @@
         <v>74</v>
       </c>
       <c r="C78">
-        <f>_xlfn.FORECAST.ETS(A78,$B$5:$B$66,$A$5:$A$66,1,1)</f>
+        <f t="shared" si="0"/>
         <v>1323557.5969044012</v>
       </c>
-      <c r="D78" s="7">
-        <f>C78-_xlfn.FORECAST.ETS.CONFINT(A78,$B$5:$B$66,$A$5:$A$66,0.95,1,1)</f>
+      <c r="D78" s="6">
+        <f t="shared" si="1"/>
         <v>190196.71129859774</v>
       </c>
-      <c r="E78" s="7">
-        <f>C78+_xlfn.FORECAST.ETS.CONFINT(A78,$B$5:$B$66,$A$5:$A$66,0.95,1,1)</f>
+      <c r="E78" s="6">
+        <f t="shared" si="2"/>
         <v>2456918.4825102044</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F79" s="7"/>
-      <c r="G79" s="7"/>
+      <c r="F79" s="6"/>
+      <c r="G79" s="6"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F80" s="7"/>
+      <c r="F80" s="6"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="55" t="s">
+      <c r="A81" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B81" s="55" t="s">
-        <v>63</v>
-      </c>
-      <c r="C81" s="55" t="s">
-        <v>64</v>
-      </c>
-      <c r="D81" s="55" t="s">
-        <v>65</v>
-      </c>
-      <c r="F81" s="7"/>
+      <c r="B81" s="49" t="s">
+        <v>59</v>
+      </c>
+      <c r="C81" s="49" t="s">
+        <v>60</v>
+      </c>
+      <c r="D81" s="49" t="s">
+        <v>61</v>
+      </c>
+      <c r="F81" s="6"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="47">
+      <c r="A82" s="13">
         <v>44256</v>
       </c>
-      <c r="B82" s="34">
-        <f>D67*$D$97</f>
+      <c r="B82" s="31">
+        <f t="shared" ref="B82:B93" si="3">D67*$D$97</f>
         <v>53857.528379768672</v>
       </c>
-      <c r="C82" s="34">
-        <f>C67*$D$97</f>
+      <c r="C82" s="31">
+        <f t="shared" ref="C82:C93" si="4">C67*$D$97</f>
         <v>763877.36900118995</v>
       </c>
-      <c r="D82" s="34">
-        <f>E67*$D$97</f>
+      <c r="D82" s="31">
+        <f t="shared" ref="D82:D93" si="5">E67*$D$97</f>
         <v>1473897.2096226113</v>
       </c>
-      <c r="E82" s="7"/>
-      <c r="F82" s="7"/>
+      <c r="E82" s="6"/>
+      <c r="F82" s="6"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="47">
+      <c r="A83" s="13">
         <v>44287</v>
       </c>
-      <c r="B83" s="34">
-        <f>D68*$D$97</f>
+      <c r="B83" s="31">
+        <f t="shared" si="3"/>
         <v>59820.965562544014</v>
       </c>
-      <c r="C83" s="34">
-        <f>C68*$D$97</f>
+      <c r="C83" s="31">
+        <f t="shared" si="4"/>
         <v>769844.00126605912</v>
       </c>
-      <c r="D83" s="34">
-        <f>E68*$D$97</f>
+      <c r="D83" s="31">
+        <f t="shared" si="5"/>
         <v>1479867.0369695742</v>
       </c>
-      <c r="E83" s="7"/>
-      <c r="F83" s="7"/>
+      <c r="E83" s="6"/>
+      <c r="F83" s="6"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="47">
+      <c r="A84" s="13">
         <v>44317</v>
       </c>
-      <c r="B84" s="34">
-        <f>D69*$D$97</f>
+      <c r="B84" s="31">
+        <f t="shared" si="3"/>
         <v>65781.917716968121</v>
       </c>
-      <c r="C84" s="34">
-        <f>C69*$D$97</f>
+      <c r="C84" s="31">
+        <f t="shared" si="4"/>
         <v>775810.63353092759</v>
       </c>
-      <c r="D84" s="34">
-        <f>E69*$D$97</f>
+      <c r="D84" s="31">
+        <f t="shared" si="5"/>
         <v>1485839.3493448871</v>
       </c>
-      <c r="E84" s="7"/>
-      <c r="F84" s="7"/>
+      <c r="E84" s="6"/>
+      <c r="F84" s="6"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="47">
+      <c r="A85" s="13">
         <v>44348</v>
       </c>
-      <c r="B85" s="34">
-        <f>D70*$D$97</f>
+      <c r="B85" s="31">
+        <f t="shared" si="3"/>
         <v>71739.67490023571</v>
       </c>
-      <c r="C85" s="34">
-        <f>C70*$D$97</f>
+      <c r="C85" s="31">
+        <f t="shared" si="4"/>
         <v>781777.26579579676</v>
       </c>
-      <c r="D85" s="34">
-        <f>E70*$D$97</f>
+      <c r="D85" s="31">
+        <f t="shared" si="5"/>
         <v>1491814.8566913579</v>
       </c>
-      <c r="E85" s="7"/>
-      <c r="F85" s="7"/>
+      <c r="E85" s="6"/>
+      <c r="F85" s="6"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="47">
+      <c r="A86" s="13">
         <v>44378</v>
       </c>
-      <c r="B86" s="34">
-        <f>D71*$D$97</f>
+      <c r="B86" s="31">
+        <f t="shared" si="3"/>
         <v>77693.527242482567</v>
       </c>
-      <c r="C86" s="34">
-        <f>C71*$D$97</f>
+      <c r="C86" s="31">
+        <f t="shared" si="4"/>
         <v>787743.89806066535</v>
       </c>
-      <c r="D86" s="34">
-        <f>E71*$D$97</f>
+      <c r="D86" s="31">
+        <f t="shared" si="5"/>
         <v>1497794.2688788483</v>
       </c>
-      <c r="E86" s="7"/>
-      <c r="F86" s="7"/>
+      <c r="E86" s="6"/>
+      <c r="F86" s="6"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="47">
+      <c r="A87" s="13">
         <v>44409</v>
       </c>
-      <c r="B87" s="34">
-        <f>D72*$D$97</f>
+      <c r="B87" s="31">
+        <f t="shared" si="3"/>
         <v>83642.76498227616</v>
       </c>
-      <c r="C87" s="34">
-        <f>C72*$D$97</f>
+      <c r="C87" s="31">
+        <f t="shared" si="4"/>
         <v>793710.53032553452</v>
       </c>
-      <c r="D87" s="34">
-        <f>E72*$D$97</f>
+      <c r="D87" s="31">
+        <f t="shared" si="5"/>
         <v>1503778.2956687929</v>
       </c>
-      <c r="E87" s="7"/>
-      <c r="F87" s="7"/>
+      <c r="E87" s="6"/>
+      <c r="F87" s="6"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="47">
+      <c r="A88" s="13">
         <v>44440</v>
       </c>
-      <c r="B88" s="34">
-        <f>D73*$D$97</f>
+      <c r="B88" s="31">
+        <f t="shared" si="3"/>
         <v>89586.678509177349</v>
       </c>
-      <c r="C88" s="34">
-        <f>C73*$D$97</f>
+      <c r="C88" s="31">
+        <f t="shared" si="4"/>
         <v>799677.16259040323</v>
       </c>
-      <c r="D88" s="34">
-        <f>E73*$D$97</f>
+      <c r="D88" s="31">
+        <f t="shared" si="5"/>
         <v>1509767.646671629</v>
       </c>
-      <c r="E88" s="7"/>
-      <c r="F88" s="7"/>
+      <c r="E88" s="6"/>
+      <c r="F88" s="6"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="47">
+      <c r="A89" s="13">
         <v>44470</v>
       </c>
-      <c r="B89" s="34">
-        <f>D74*$D$97</f>
+      <c r="B89" s="31">
+        <f t="shared" si="3"/>
         <v>95524.558413384468</v>
       </c>
-      <c r="C89" s="34">
-        <f>C74*$D$97</f>
+      <c r="C89" s="31">
+        <f t="shared" si="4"/>
         <v>805643.79485527228</v>
       </c>
-      <c r="D89" s="34">
-        <f>E74*$D$97</f>
+      <c r="D89" s="31">
+        <f t="shared" si="5"/>
         <v>1515763.0312971601</v>
       </c>
-      <c r="E89" s="7"/>
-      <c r="F89" s="7"/>
+      <c r="E89" s="6"/>
+      <c r="F89" s="6"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="47">
+      <c r="A90" s="13">
         <v>44501</v>
       </c>
-      <c r="B90" s="34">
-        <f>D75*$D$97</f>
+      <c r="B90" s="31">
+        <f t="shared" si="3"/>
         <v>101455.69554242518</v>
       </c>
-      <c r="C90" s="34">
-        <f>C75*$D$97</f>
+      <c r="C90" s="31">
+        <f t="shared" si="4"/>
         <v>811610.42712014087</v>
       </c>
-      <c r="D90" s="34">
-        <f>E75*$D$97</f>
+      <c r="D90" s="31">
+        <f t="shared" si="5"/>
         <v>1521765.1586978564</v>
       </c>
-      <c r="E90" s="7"/>
-      <c r="F90" s="7"/>
+      <c r="E90" s="6"/>
+      <c r="F90" s="6"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="47">
+      <c r="A91" s="13">
         <v>44531</v>
       </c>
-      <c r="B91" s="34">
-        <f>D76*$D$97</f>
+      <c r="B91" s="31">
+        <f t="shared" si="3"/>
         <v>107379.38106489564</v>
       </c>
-      <c r="C91" s="34">
-        <f>C76*$D$97</f>
+      <c r="C91" s="31">
+        <f t="shared" si="4"/>
         <v>817577.05938501004</v>
       </c>
-      <c r="D91" s="34">
-        <f>E76*$D$97</f>
+      <c r="D91" s="31">
+        <f t="shared" si="5"/>
         <v>1527774.7377051245</v>
       </c>
-      <c r="E91" s="7"/>
+      <c r="E91" s="6"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="47">
+      <c r="A92" s="13">
         <v>44562</v>
       </c>
-      <c r="B92" s="34">
-        <f>D77*$D$97</f>
+      <c r="B92" s="31">
+        <f t="shared" si="3"/>
         <v>113294.90654120463</v>
       </c>
-      <c r="C92" s="34">
-        <f>C77*$D$97</f>
+      <c r="C92" s="31">
+        <f t="shared" si="4"/>
         <v>823543.69164987863</v>
       </c>
-      <c r="D92" s="34">
-        <f>E77*$D$97</f>
+      <c r="D92" s="31">
+        <f t="shared" si="5"/>
         <v>1533792.4767585527</v>
       </c>
-      <c r="E92" s="7"/>
+      <c r="E92" s="6"/>
     </row>
     <row r="93" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="56">
+      <c r="A93" s="50">
         <v>44593</v>
       </c>
-      <c r="B93" s="57">
-        <f>D78*$D$97</f>
+      <c r="B93" s="51">
+        <f t="shared" si="3"/>
         <v>119201.56400130966</v>
       </c>
-      <c r="C93" s="57">
-        <f>C78*$D$97</f>
+      <c r="C93" s="51">
+        <f t="shared" si="4"/>
         <v>829510.3239147478</v>
       </c>
-      <c r="D93" s="57">
-        <f>E78*$D$97</f>
+      <c r="D93" s="51">
+        <f t="shared" si="5"/>
         <v>1539819.0838281859</v>
       </c>
-      <c r="E93" s="7"/>
+      <c r="E93" s="6"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="B94" s="38">
+      <c r="A94" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="B94" s="35">
         <f>SUM(B82:B93)</f>
         <v>1038979.1628566722</v>
       </c>
-      <c r="C94" s="38">
-        <f t="shared" ref="C94:D94" si="0">SUM(C82:C93)</f>
+      <c r="C94" s="35">
+        <f t="shared" ref="C94:D94" si="6">SUM(C82:C93)</f>
         <v>9560326.1574956253</v>
       </c>
-      <c r="D94" s="38">
-        <f t="shared" si="0"/>
+      <c r="D94" s="35">
+        <f t="shared" si="6"/>
         <v>18081673.152134579</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="D96" s="7">
+      <c r="A96" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="D96" s="6">
         <f>AVERAGE(B5:B66)</f>
         <v>899281.92887096771</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="B97" s="7"/>
-      <c r="D97" s="54">
+      <c r="A97" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="B97" s="6"/>
+      <c r="D97" s="6">
         <f>AVERAGE(B64:B66)/D96</f>
         <v>0.62672778718118927</v>
       </c>
@@ -9200,7 +9191,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A252104F-5C6D-411C-9F3F-B8BB17F13FE0}">
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.21875" style="1" customWidth="1"/>
@@ -9215,34 +9206,39 @@
     <col min="13" max="13" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="59" t="s">
-        <v>73</v>
-      </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="60" t="s">
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.4">
+      <c r="A1" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="55" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="61" t="s">
+      <c r="B4" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="61" t="s">
+      <c r="C4" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="61" t="s">
+      <c r="D4" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="61" t="s">
+      <c r="E4" s="38" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="13">
         <v>42370</v>
       </c>
       <c r="B5">
@@ -9253,8 +9249,8 @@
         <v>649918.78</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="13">
         <v>42401</v>
       </c>
       <c r="B6">
@@ -9270,8 +9266,8 @@
         <v>37.11</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="13">
         <v>42430</v>
       </c>
       <c r="B7">
@@ -9287,8 +9283,8 @@
         <v>-62.02</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="13">
         <v>42461</v>
       </c>
       <c r="B8">
@@ -9304,8 +9300,8 @@
         <v>-67.319999999999993</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="13">
         <v>42491</v>
       </c>
       <c r="B9">
@@ -9321,8 +9317,8 @@
         <v>438.91</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="13">
         <v>42522</v>
       </c>
       <c r="B10">
@@ -9338,8 +9334,8 @@
         <v>-12.99</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="13">
         <v>42552</v>
       </c>
       <c r="B11">
@@ -9355,8 +9351,8 @@
         <v>-12.27</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="13">
         <v>42583</v>
       </c>
       <c r="B12">
@@ -9371,9 +9367,12 @@
       <c r="E12">
         <v>20.34</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
+      <c r="H12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="13">
         <v>42614</v>
       </c>
       <c r="B13">
@@ -9389,8 +9388,8 @@
         <v>3.64</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="13">
         <v>42644</v>
       </c>
       <c r="B14">
@@ -9406,8 +9405,8 @@
         <v>9.9600000000000009</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="13">
         <v>42675</v>
       </c>
       <c r="B15">
@@ -9423,8 +9422,8 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="13">
         <v>42705</v>
       </c>
       <c r="B16">
@@ -9441,7 +9440,7 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
+      <c r="A17" s="13">
         <v>42736</v>
       </c>
       <c r="B17">
@@ -9458,7 +9457,7 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
+      <c r="A18" s="13">
         <v>42767</v>
       </c>
       <c r="B18">
@@ -9475,7 +9474,7 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="1">
+      <c r="A19" s="13">
         <v>42795</v>
       </c>
       <c r="B19">
@@ -9492,7 +9491,7 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
+      <c r="A20" s="13">
         <v>42826</v>
       </c>
       <c r="B20">
@@ -9509,7 +9508,7 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="1">
+      <c r="A21" s="13">
         <v>42856</v>
       </c>
       <c r="B21">
@@ -9526,7 +9525,7 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
+      <c r="A22" s="13">
         <v>42887</v>
       </c>
       <c r="B22">
@@ -9543,7 +9542,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1">
+      <c r="A23" s="13">
         <v>42917</v>
       </c>
       <c r="B23">
@@ -9560,7 +9559,7 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
+      <c r="A24" s="13">
         <v>42948</v>
       </c>
       <c r="B24">
@@ -9577,7 +9576,7 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
+      <c r="A25" s="13">
         <v>42979</v>
       </c>
       <c r="B25">
@@ -9594,7 +9593,7 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
+      <c r="A26" s="13">
         <v>43009</v>
       </c>
       <c r="B26">
@@ -9611,7 +9610,7 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
+      <c r="A27" s="13">
         <v>43040</v>
       </c>
       <c r="B27">
@@ -9628,7 +9627,7 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="1">
+      <c r="A28" s="13">
         <v>43070</v>
       </c>
       <c r="B28">
@@ -9645,7 +9644,7 @@
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="1">
+      <c r="A29" s="13">
         <v>43101</v>
       </c>
       <c r="B29">
@@ -9662,7 +9661,7 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="1">
+      <c r="A30" s="13">
         <v>43132</v>
       </c>
       <c r="B30">
@@ -9679,7 +9678,7 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="1">
+      <c r="A31" s="13">
         <v>43160</v>
       </c>
       <c r="B31">
@@ -9696,7 +9695,7 @@
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="1">
+      <c r="A32" s="13">
         <v>43191</v>
       </c>
       <c r="B32">
@@ -9713,7 +9712,7 @@
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="1">
+      <c r="A33" s="13">
         <v>43221</v>
       </c>
       <c r="B33">
@@ -9730,7 +9729,7 @@
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="1">
+      <c r="A34" s="13">
         <v>43252</v>
       </c>
       <c r="B34">
@@ -9747,7 +9746,7 @@
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="1">
+      <c r="A35" s="13">
         <v>43282</v>
       </c>
       <c r="B35">
@@ -9764,7 +9763,7 @@
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="1">
+      <c r="A36" s="13">
         <v>43313</v>
       </c>
       <c r="B36">
@@ -9781,7 +9780,7 @@
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="1">
+      <c r="A37" s="13">
         <v>43344</v>
       </c>
       <c r="B37">
@@ -9798,7 +9797,7 @@
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="1">
+      <c r="A38" s="13">
         <v>43374</v>
       </c>
       <c r="B38">
@@ -9815,7 +9814,7 @@
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="1">
+      <c r="A39" s="13">
         <v>43405</v>
       </c>
       <c r="B39">
@@ -9832,7 +9831,7 @@
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="1">
+      <c r="A40" s="13">
         <v>43435</v>
       </c>
       <c r="B40">
@@ -9849,7 +9848,7 @@
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="1">
+      <c r="A41" s="13">
         <v>43466</v>
       </c>
       <c r="B41">
@@ -9866,7 +9865,7 @@
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="1">
+      <c r="A42" s="13">
         <v>43497</v>
       </c>
       <c r="B42">
@@ -9883,7 +9882,7 @@
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="1">
+      <c r="A43" s="13">
         <v>43525</v>
       </c>
       <c r="B43">
@@ -9900,7 +9899,7 @@
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="1">
+      <c r="A44" s="13">
         <v>43556</v>
       </c>
       <c r="B44">
@@ -9917,7 +9916,7 @@
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="1">
+      <c r="A45" s="13">
         <v>43586</v>
       </c>
       <c r="B45">
@@ -9934,7 +9933,7 @@
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="1">
+      <c r="A46" s="13">
         <v>43617</v>
       </c>
       <c r="B46">
@@ -9951,7 +9950,7 @@
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="1">
+      <c r="A47" s="13">
         <v>43647</v>
       </c>
       <c r="B47">
@@ -9968,7 +9967,7 @@
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="1">
+      <c r="A48" s="13">
         <v>43678</v>
       </c>
       <c r="B48">
@@ -9985,7 +9984,7 @@
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="1">
+      <c r="A49" s="13">
         <v>43709</v>
       </c>
       <c r="B49">
@@ -10002,7 +10001,7 @@
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="1">
+      <c r="A50" s="13">
         <v>43739</v>
       </c>
       <c r="B50">
@@ -10019,7 +10018,7 @@
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="1">
+      <c r="A51" s="13">
         <v>43770</v>
       </c>
       <c r="B51">
@@ -10036,7 +10035,7 @@
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" s="1">
+      <c r="A52" s="13">
         <v>43800</v>
       </c>
       <c r="B52">
@@ -10053,7 +10052,7 @@
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53" s="1">
+      <c r="A53" s="13">
         <v>43831</v>
       </c>
       <c r="B53">
@@ -10070,7 +10069,7 @@
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="1">
+      <c r="A54" s="13">
         <v>43862</v>
       </c>
       <c r="B54">
@@ -10087,7 +10086,7 @@
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55" s="1">
+      <c r="A55" s="13">
         <v>43891</v>
       </c>
       <c r="B55">
@@ -10104,7 +10103,7 @@
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" s="1">
+      <c r="A56" s="13">
         <v>43922</v>
       </c>
       <c r="B56">
@@ -10121,7 +10120,7 @@
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" s="1">
+      <c r="A57" s="13">
         <v>43952</v>
       </c>
       <c r="B57">
@@ -10138,7 +10137,7 @@
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" s="1">
+      <c r="A58" s="13">
         <v>43983</v>
       </c>
       <c r="B58">
@@ -10155,7 +10154,7 @@
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59" s="1">
+      <c r="A59" s="13">
         <v>44013</v>
       </c>
       <c r="B59">
@@ -10172,7 +10171,7 @@
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A60" s="1">
+      <c r="A60" s="13">
         <v>44044</v>
       </c>
       <c r="B60">
@@ -10189,7 +10188,7 @@
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" s="1">
+      <c r="A61" s="13">
         <v>44075</v>
       </c>
       <c r="B61">
@@ -10206,7 +10205,7 @@
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A62" s="1">
+      <c r="A62" s="13">
         <v>44105</v>
       </c>
       <c r="B62">
@@ -10223,7 +10222,7 @@
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A63" s="1">
+      <c r="A63" s="13">
         <v>44136</v>
       </c>
       <c r="B63">
@@ -10240,7 +10239,7 @@
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64" s="1">
+      <c r="A64" s="13">
         <v>44166</v>
       </c>
       <c r="B64">
@@ -10257,7 +10256,7 @@
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A65" s="5">
+      <c r="A65" s="56">
         <v>44197</v>
       </c>
       <c r="B65">
@@ -10274,29 +10273,30 @@
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A66" s="8">
+      <c r="A66" s="57">
         <v>44228</v>
       </c>
       <c r="B66">
         <v>62</v>
       </c>
-      <c r="C66" s="9">
+      <c r="C66" s="7">
         <v>526266.9</v>
       </c>
-      <c r="D66" s="9">
+      <c r="D66" s="7">
         <v>513021.58</v>
       </c>
-      <c r="E66" s="9">
+      <c r="E66" s="7">
         <v>2.58</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B67" s="7"/>
+      <c r="B67" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>

--- a/Global+Electronics+Retailer/Excel_Files/Revenue_Forecast.xlsx
+++ b/Global+Electronics+Retailer/Excel_Files/Revenue_Forecast.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Darren Cruz\Documents\GitHub\Global-Electronics-Retail-Performace-Analysis\Global+Electronics+Retailer\Excel_Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE5CAE03-3375-403B-AF2C-67669164EA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDDE8887-1DEE-495B-B7E5-426C6B900C1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CAC95C2E-2B41-4FED-8B73-E3EFD4DDAC30}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="81">
   <si>
     <t>Month</t>
   </si>
@@ -299,17 +299,24 @@
   <si>
     <t>s</t>
   </si>
+  <si>
+    <t>Actual Last 12 Months:</t>
+  </si>
+  <si>
+    <t>vs. Last 12 Months:</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="mmm\ yyyy"/>
     <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="169" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -376,6 +383,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -612,10 +626,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -716,9 +731,12 @@
     <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="21">
     <dxf>
@@ -5531,6 +5549,32 @@
         <v>-4984256.4692179952</v>
       </c>
     </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" s="58">
+        <f>SUM(INDEX(Table4[Revenue], COUNT(Table4[Revenue])-11):INDEX(Table4[Revenue],COUNT(Table4[Revenue])))</f>
+        <v>6037589.9299999997</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" s="59">
+        <f>D21/$E$22-1</f>
+        <v>-0.34837131006707156</v>
+      </c>
+      <c r="E23" s="59">
+        <f>E21/$E$22-1</f>
+        <v>-0.24207014034859564</v>
+      </c>
+      <c r="F23" s="59">
+        <f>F21/$E$22-1</f>
+        <v>-4.7177567310273449E-2</v>
+      </c>
+    </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="26" t="s">
         <v>64</v>
